--- a/team/jin-qinhao/Take-Home-Exercise2/data/Name your insight (2).xlsx
+++ b/team/jin-qinhao/Take-Home-Exercise2/data/Name your insight (2).xlsx
@@ -16,14 +16,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.00"/>
     <numFmt numFmtId="165" formatCode="MM/yyyy"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.00"/>
     <numFmt numFmtId="165" formatCode="MM/yyyy"/>
-    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="164" formatCode="0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -42,6 +43,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF3A56"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -67,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -82,6 +90,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -376,44 +385,99 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:S141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Visitor Arrivals</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Tourism Receipts: YTD: YoY</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Tourism Receipts: YTD</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Visitor Arrivals: China</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Average Length of Stay</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Tourist Expenditure Per Capita</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Visitor Arrivals: Malaysia</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Visitor Arrivals: India</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Hotel Room Occupancy Rate</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Tourist Expenditure Per Capita</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Tourism Receipts</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Average Length of Stay</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Visitor Arrivals</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Visitor Arrivals: China</t>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Tourist Expenditure Per Capita: China</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Tourist Expenditure Per Capita: India</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Tourist Expenditure Per Capita: Malaysia</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Average Length of Stay: Malaysia</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Average Length of Stay: China</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Average Length of Stay: India</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>No of Hotel Room Stock</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Average Length of Stay</t>
         </is>
       </c>
     </row>
@@ -454,6 +518,61 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
@@ -472,6 +591,17 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -486,30 +616,85 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>Quarterly, ending "Mar, June, Sep, Dec"</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly, ending "Mar, June, Sep, Dec"</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Annual, ending "Dec" of each year</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Annual, ending "Dec" of each year</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Annual, ending "Dec" of each year</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>Annual, ending "Dec" of each year</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Annual, ending "Dec" of each year</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly, ending "Mar, June, Sep, Dec"</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
@@ -523,37 +708,92 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>SGD mn</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>SGD</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>SGD mn</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>SGD</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Person</t>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>Day</t>
         </is>
       </c>
     </row>
@@ -598,6 +838,61 @@
           <t>Singapore Tourism Board</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Singapore Tourism Board</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Singapore Tourism Board</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Singapore Tourism Board</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Singapore Tourism Board</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Singapore Tourism Board</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Singapore Tourism Board</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>Singapore Tourism Board</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Singapore Tourism Board</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Singapore Tourism Board</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Singapore Tourism Board</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>Singapore Tourism Board</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -640,6 +935,61 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -649,37 +999,92 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>36573201 (SQDA)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>541546977 (SQWAAAAAAAAAEW)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>494353277 (SQWAAAAAAAAAEO)</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>36573801 (SQDD)</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
           <t>36593701 (SQLA)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>36567601 (SQCBB)</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>36575701 (SQDJC)</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>36577801 (SQDM)</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>400503207 (SQWAAAAAAAAACY)</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>36567601 (SQCBB)</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>36564801 (SQBDA)</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>36598401 (SQUA)</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>36573201 (SQDA)</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>36573801 (SQDD)</t>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>36571701 (SQCBEG)</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>36571901 (SQCBEI)</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>36571401 (SQCBED)</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>36594101 (SQLAAE)</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>36594501 (SQLAAI)</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>36594901 (SQLAAM)</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>522640837 (SQWAAAAAAAAAEV)</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>36593701 (SQLA)</t>
         </is>
       </c>
     </row>
@@ -691,37 +1096,92 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>SR193732</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>SR225833897</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>SR171642007</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>SR193743</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>SR564330</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>SR87332</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>SR193760</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>SR193752</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>SR113190827</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>SR87332</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>SR87321</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>SR426143</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>SR193732</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>SR193743</t>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>SR87376</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>SR87378</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>SR87373</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>SR564334</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SR564338</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>SR564342</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>SR215088307</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>SR564330</t>
         </is>
       </c>
     </row>
@@ -738,6 +1198,17 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -752,6 +1223,17 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -766,6 +1248,17 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -774,25 +1267,58 @@
         </is>
       </c>
       <c r="B13" s="4">
+        <v>28491</v>
+      </c>
+      <c r="C13" s="4">
+        <v>39508</v>
+      </c>
+      <c r="D13" s="4">
+        <v>39142</v>
+      </c>
+      <c r="E13" s="4">
+        <v>28491</v>
+      </c>
+      <c r="F13" s="4">
         <v>33604</v>
       </c>
-      <c r="C13" s="4">
+      <c r="G13" s="4">
+        <v>35034</v>
+      </c>
+      <c r="H13" s="4">
+        <v>34700</v>
+      </c>
+      <c r="I13" s="4">
+        <v>28491</v>
+      </c>
+      <c r="J13" s="4">
         <v>39083</v>
       </c>
-      <c r="D13" s="4">
+      <c r="K13" s="4">
+        <v>30651</v>
+      </c>
+      <c r="L13" s="4">
         <v>35034</v>
       </c>
-      <c r="E13" s="4">
-        <v>33573</v>
-      </c>
-      <c r="F13" s="4">
-        <v>30651</v>
-      </c>
-      <c r="G13" s="4">
-        <v>28491</v>
-      </c>
-      <c r="H13" s="4">
-        <v>28491</v>
+      <c r="M13" s="4">
+        <v>35034</v>
+      </c>
+      <c r="N13" s="4">
+        <v>36130</v>
+      </c>
+      <c r="O13" s="4">
+        <v>36526</v>
+      </c>
+      <c r="P13" s="4">
+        <v>36526</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>36526</v>
+      </c>
+      <c r="R13" s="4">
+        <v>39508</v>
+      </c>
+      <c r="S13" s="4">
+        <v>33604</v>
       </c>
     </row>
     <row r="14">
@@ -802,25 +1328,58 @@
         </is>
       </c>
       <c r="B14" s="4">
+        <v>46054</v>
+      </c>
+      <c r="C14" s="4">
+        <v>45901</v>
+      </c>
+      <c r="D14" s="4">
+        <v>45901</v>
+      </c>
+      <c r="E14" s="4">
+        <v>46054</v>
+      </c>
+      <c r="F14" s="4">
+        <v>46054</v>
+      </c>
+      <c r="G14" s="4">
+        <v>45627</v>
+      </c>
+      <c r="H14" s="4">
+        <v>46054</v>
+      </c>
+      <c r="I14" s="4">
+        <v>46054</v>
+      </c>
+      <c r="J14" s="4">
         <v>46023</v>
       </c>
-      <c r="C14" s="4">
-        <v>46023</v>
-      </c>
-      <c r="D14" s="4">
+      <c r="K14" s="4">
+        <v>45992</v>
+      </c>
+      <c r="L14" s="4">
         <v>45627</v>
       </c>
-      <c r="E14" s="4">
+      <c r="M14" s="4">
         <v>45627</v>
       </c>
-      <c r="F14" s="4">
+      <c r="N14" s="4">
+        <v>45627</v>
+      </c>
+      <c r="O14" s="4">
+        <v>46054</v>
+      </c>
+      <c r="P14" s="4">
+        <v>46054</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>46054</v>
+      </c>
+      <c r="R14" s="4">
         <v>45992</v>
       </c>
-      <c r="G14" s="4">
-        <v>46023</v>
-      </c>
-      <c r="H14" s="4">
-        <v>46023</v>
+      <c r="S14" s="4">
+        <v>46054</v>
       </c>
     </row>
     <row r="15">
@@ -830,25 +1389,58 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <v>46083</v>
+        <v>46097</v>
       </c>
       <c r="C15" s="5">
+        <v>46056</v>
+      </c>
+      <c r="D15" s="5">
+        <v>46056</v>
+      </c>
+      <c r="E15" s="5">
+        <v>46097</v>
+      </c>
+      <c r="F15" s="5">
+        <v>46097</v>
+      </c>
+      <c r="G15" s="5">
+        <v>45761</v>
+      </c>
+      <c r="H15" s="5">
+        <v>46097</v>
+      </c>
+      <c r="I15" s="5">
+        <v>46097</v>
+      </c>
+      <c r="J15" s="5">
         <v>46079</v>
       </c>
-      <c r="D15" s="5">
+      <c r="K15" s="5">
+        <v>46097</v>
+      </c>
+      <c r="L15" s="5">
         <v>45761</v>
       </c>
-      <c r="E15" s="5">
+      <c r="M15" s="5">
         <v>45761</v>
       </c>
-      <c r="F15" s="5">
-        <v>46069</v>
-      </c>
-      <c r="G15" s="5">
-        <v>46069</v>
-      </c>
-      <c r="H15" s="5">
-        <v>46069</v>
+      <c r="N15" s="5">
+        <v>45761</v>
+      </c>
+      <c r="O15" s="5">
+        <v>46097</v>
+      </c>
+      <c r="P15" s="5">
+        <v>46097</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>46097</v>
+      </c>
+      <c r="R15" s="5">
+        <v>46056</v>
+      </c>
+      <c r="S15" s="5">
+        <v>46097</v>
       </c>
     </row>
     <row r="16">
@@ -862,20 +1454,55 @@
           <t>[COVID-19-IMPACT]</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>[COVID-19-IMPACT]</t>
         </is>
       </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>[COVID-19-IMPACT]</t>
         </is>
       </c>
+      <c r="G16" s="6"/>
       <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>[COVID-19-IMPACT]</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>[COVID-19-IMPACT]</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>[COVID-19-IMPACT]</t>
+        </is>
+      </c>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>[COVID-19-IMPACT]</t>
+        </is>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>[COVID-19-IMPACT]</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>[COVID-19-IMPACT]</t>
+        </is>
+      </c>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6" t="inlineStr">
         <is>
           <t>[COVID-19-IMPACT]</t>
         </is>
@@ -894,6 +1521,17 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3"/>
+      <c r="R17" s="3"/>
+      <c r="S17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -902,25 +1540,58 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <v>9.261770936454546</v>
+        <v>1044833.972972973</v>
       </c>
       <c r="C18" s="7">
+        <v>63.32254572333337</v>
+      </c>
+      <c r="D18" s="7">
+        <v>13016.61363230389</v>
+      </c>
+      <c r="E18" s="7">
+        <v>174087.3063063063</v>
+      </c>
+      <c r="F18" s="7">
+        <v>9.208840206306308</v>
+      </c>
+      <c r="G18" s="7">
+        <v>2098.780516466</v>
+      </c>
+      <c r="H18" s="7">
+        <v>74749.36036036036</v>
+      </c>
+      <c r="I18" s="7">
+        <v>78991.04504504504</v>
+      </c>
+      <c r="J18" s="7">
         <v>76.8948708820909</v>
       </c>
-      <c r="D18" s="7">
-        <v>2098.780516466</v>
-      </c>
-      <c r="E18" s="7">
-        <v>20680.113317019</v>
-      </c>
-      <c r="F18" s="7">
-        <v>5.60709143</v>
-      </c>
-      <c r="G18" s="7">
-        <v>1040687.054545455</v>
-      </c>
-      <c r="H18" s="7">
-        <v>171739.6636363636</v>
+      <c r="K18" s="7">
+        <v>5.607091402</v>
+      </c>
+      <c r="L18" s="7">
+        <v>2210.209549848</v>
+      </c>
+      <c r="M18" s="7">
+        <v>1375.306732667</v>
+      </c>
+      <c r="N18" s="7">
+        <v>954.5680238809998</v>
+      </c>
+      <c r="O18" s="7">
+        <v>4.522510149639642</v>
+      </c>
+      <c r="P18" s="7">
+        <v>11.60582967342342</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>15.42897740072072</v>
+      </c>
+      <c r="R18" s="7">
+        <v>62326.50450450434</v>
+      </c>
+      <c r="S18" s="7">
+        <v>9.208840206306308</v>
       </c>
     </row>
     <row r="19">
@@ -930,25 +1601,58 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <v>144.1470927121989</v>
+        <v>370679114272.9355</v>
       </c>
       <c r="C19" s="7">
+        <v>33718.54812357202</v>
+      </c>
+      <c r="D19" s="7">
+        <v>85456202.05871888</v>
+      </c>
+      <c r="E19" s="7">
+        <v>18413283697.32351</v>
+      </c>
+      <c r="F19" s="7">
+        <v>143.1476490870074</v>
+      </c>
+      <c r="G19" s="7">
+        <v>1705539.521867197</v>
+      </c>
+      <c r="H19" s="7">
+        <v>1808353342.868959</v>
+      </c>
+      <c r="I19" s="7">
+        <v>2182336779.534316</v>
+      </c>
+      <c r="J19" s="7">
         <v>159.7887883352196</v>
       </c>
-      <c r="D19" s="7">
-        <v>1705539.521867197</v>
-      </c>
-      <c r="E19" s="7">
-        <v>102661837.5217181</v>
-      </c>
-      <c r="F19" s="7">
-        <v>35.17572745683988</v>
-      </c>
-      <c r="G19" s="7">
-        <v>372153471879.6115</v>
-      </c>
-      <c r="H19" s="7">
-        <v>17964836252.72068</v>
+      <c r="K19" s="7">
+        <v>35.17572758889354</v>
+      </c>
+      <c r="L19" s="7">
+        <v>2970384.702605994</v>
+      </c>
+      <c r="M19" s="7">
+        <v>47053.10939929381</v>
+      </c>
+      <c r="N19" s="7">
+        <v>454730.4743068273</v>
+      </c>
+      <c r="O19" s="7">
+        <v>29.19219204868003</v>
+      </c>
+      <c r="P19" s="7">
+        <v>220.6829120667696</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>337.3065331564245</v>
+      </c>
+      <c r="R19" s="7">
+        <v>9993338.306308575</v>
+      </c>
+      <c r="S19" s="7">
+        <v>143.1476490870074</v>
       </c>
     </row>
     <row r="20">
@@ -958,25 +1662,58 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <v>12.00612729868374</v>
+        <v>608834.2256090203</v>
       </c>
       <c r="C20" s="7">
+        <v>183.6261095911255</v>
+      </c>
+      <c r="D20" s="7">
+        <v>9244.252379652931</v>
+      </c>
+      <c r="E20" s="7">
+        <v>135695.5551863196</v>
+      </c>
+      <c r="F20" s="7">
+        <v>11.96443266883171</v>
+      </c>
+      <c r="G20" s="7">
+        <v>1305.963062979653</v>
+      </c>
+      <c r="H20" s="7">
+        <v>42524.73801058578</v>
+      </c>
+      <c r="I20" s="7">
+        <v>46715.48757675891</v>
+      </c>
+      <c r="J20" s="7">
         <v>12.64075900945903</v>
       </c>
-      <c r="D20" s="7">
-        <v>1305.963062979653</v>
-      </c>
-      <c r="E20" s="7">
-        <v>10132.21779877032</v>
-      </c>
-      <c r="F20" s="7">
-        <v>5.930912868761426</v>
-      </c>
-      <c r="G20" s="7">
-        <v>610043.8278350265</v>
-      </c>
-      <c r="H20" s="7">
-        <v>134032.9670369222</v>
+      <c r="K20" s="7">
+        <v>5.930912879894084</v>
+      </c>
+      <c r="L20" s="7">
+        <v>1723.480403893817</v>
+      </c>
+      <c r="M20" s="7">
+        <v>216.9172869996622</v>
+      </c>
+      <c r="N20" s="7">
+        <v>674.3370628304715</v>
+      </c>
+      <c r="O20" s="7">
+        <v>5.402979923031366</v>
+      </c>
+      <c r="P20" s="7">
+        <v>14.85540009783545</v>
+      </c>
+      <c r="Q20" s="7">
+        <v>18.36590681552165</v>
+      </c>
+      <c r="R20" s="7">
+        <v>3161.22417843287</v>
+      </c>
+      <c r="S20" s="7">
+        <v>11.96443266883171</v>
       </c>
     </row>
     <row r="21">
@@ -986,25 +1723,58 @@
         </is>
       </c>
       <c r="B21" s="7">
-        <v>2.237796487383857</v>
+        <v>-0.8159552623027665</v>
       </c>
       <c r="C21" s="7">
+        <v>2.32556666216772</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.340000246554436</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.003943980073930882</v>
+      </c>
+      <c r="F21" s="7">
+        <v>2.252762039055943</v>
+      </c>
+      <c r="G21" s="7">
+        <v>2.927113293110208</v>
+      </c>
+      <c r="H21" s="7">
+        <v>-0.8690383490793696</v>
+      </c>
+      <c r="I21" s="7">
+        <v>-0.3410814821178095</v>
+      </c>
+      <c r="J21" s="7">
         <v>-1.238631139729319</v>
       </c>
-      <c r="D21" s="7">
-        <v>2.927113293110208</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.189766453533627</v>
-      </c>
-      <c r="F21" s="7">
-        <v>3.114367401624683</v>
-      </c>
-      <c r="G21" s="7">
-        <v>-0.8018246972679557</v>
-      </c>
-      <c r="H21" s="7">
-        <v>-0.01743676279338081</v>
+      <c r="K21" s="7">
+        <v>3.114367399272213</v>
+      </c>
+      <c r="L21" s="7">
+        <v>1.787456109831896</v>
+      </c>
+      <c r="M21" s="7">
+        <v>0.5845511011625032</v>
+      </c>
+      <c r="N21" s="7">
+        <v>2.89271195072922</v>
+      </c>
+      <c r="O21" s="7">
+        <v>3.368718247223009</v>
+      </c>
+      <c r="P21" s="7">
+        <v>2.002297945815037</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>1.681102603102276</v>
+      </c>
+      <c r="R21" s="7">
+        <v>0.1398951025168347</v>
+      </c>
+      <c r="S21" s="7">
+        <v>2.252762039055943</v>
       </c>
     </row>
     <row r="22">
@@ -1014,25 +1784,58 @@
         </is>
       </c>
       <c r="B22" s="7">
-        <v>4.461390077797033</v>
+        <v>-0.9471175072620199</v>
       </c>
       <c r="C22" s="7">
+        <v>5.043368750908593</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-1.251465473338307</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.313853710919364</v>
+      </c>
+      <c r="F22" s="7">
+        <v>4.536331596368695</v>
+      </c>
+      <c r="G22" s="7">
+        <v>8.866424091120461</v>
+      </c>
+      <c r="H22" s="7">
+        <v>-0.7297452276775149</v>
+      </c>
+      <c r="I22" s="7">
+        <v>-0.3618724783366813</v>
+      </c>
+      <c r="J22" s="7">
         <v>0.6869351827144112</v>
       </c>
-      <c r="D22" s="7">
-        <v>8.866424091120461</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.1126822008046435</v>
-      </c>
-      <c r="F22" s="7">
-        <v>9.769192741647661</v>
-      </c>
-      <c r="G22" s="7">
-        <v>-0.9702198622473568</v>
-      </c>
-      <c r="H22" s="7">
-        <v>-1.343972230299788</v>
+      <c r="K22" s="7">
+        <v>9.769192730025416</v>
+      </c>
+      <c r="L22" s="7">
+        <v>2.182496317141055</v>
+      </c>
+      <c r="M22" s="7">
+        <v>-1.141058108516518</v>
+      </c>
+      <c r="N22" s="7">
+        <v>8.714470390455812</v>
+      </c>
+      <c r="O22" s="7">
+        <v>13.18010941721864</v>
+      </c>
+      <c r="P22" s="7">
+        <v>3.311469956312041</v>
+      </c>
+      <c r="Q22" s="7">
+        <v>1.048405237458138</v>
+      </c>
+      <c r="R22" s="7">
+        <v>-0.8657898676692701</v>
+      </c>
+      <c r="S22" s="7">
+        <v>4.536331596368695</v>
       </c>
     </row>
     <row r="23">
@@ -1042,25 +1845,58 @@
         </is>
       </c>
       <c r="B23" s="7">
-        <v>1.296310109703463</v>
+        <v>0.5827090632176153</v>
       </c>
       <c r="C23" s="7">
+        <v>2.899853559163875</v>
+      </c>
+      <c r="D23" s="7">
+        <v>0.7101887357792561</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.7794684062005275</v>
+      </c>
+      <c r="F23" s="7">
+        <v>1.299233388873263</v>
+      </c>
+      <c r="G23" s="7">
+        <v>0.62224851657127</v>
+      </c>
+      <c r="H23" s="7">
+        <v>0.5688976842822148</v>
+      </c>
+      <c r="I23" s="7">
+        <v>0.5914023235180541</v>
+      </c>
+      <c r="J23" s="7">
         <v>0.1643901454603146</v>
       </c>
-      <c r="D23" s="7">
-        <v>0.62224851657127</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.489949820073368</v>
-      </c>
-      <c r="F23" s="7">
-        <v>1.057752123860307</v>
-      </c>
-      <c r="G23" s="7">
-        <v>0.5861933471455336</v>
-      </c>
-      <c r="H23" s="7">
-        <v>0.7804427014642323</v>
+      <c r="K23" s="7">
+        <v>1.057752131127839</v>
+      </c>
+      <c r="L23" s="7">
+        <v>0.779781448330247</v>
+      </c>
+      <c r="M23" s="7">
+        <v>0.1577228423647832</v>
+      </c>
+      <c r="N23" s="7">
+        <v>0.7064316486202946</v>
+      </c>
+      <c r="O23" s="7">
+        <v>1.194686080132265</v>
+      </c>
+      <c r="P23" s="7">
+        <v>1.279994667839502</v>
+      </c>
+      <c r="Q23" s="7">
+        <v>1.190351527422922</v>
+      </c>
+      <c r="R23" s="7">
+        <v>0.05072038298256255</v>
+      </c>
+      <c r="S23" s="7">
+        <v>1.299233388873263</v>
       </c>
     </row>
     <row r="24">
@@ -1070,25 +1906,58 @@
         </is>
       </c>
       <c r="B24" s="7">
+        <v>750</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-89.46434057</v>
+      </c>
+      <c r="D24" s="7">
+        <v>424.51831782</v>
+      </c>
+      <c r="E24" s="7">
+        <v>18</v>
+      </c>
+      <c r="F24" s="7">
         <v>3.09550355</v>
       </c>
-      <c r="C24" s="7">
+      <c r="G24" s="7">
+        <v>1429.75063841</v>
+      </c>
+      <c r="H24" s="7">
+        <v>96</v>
+      </c>
+      <c r="I24" s="7">
+        <v>12</v>
+      </c>
+      <c r="J24" s="7">
         <v>40.16224463</v>
       </c>
-      <c r="D24" s="7">
-        <v>1429.75063841</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1893.63105965</v>
-      </c>
-      <c r="F24" s="7">
+      <c r="K24" s="7">
         <v>3.33013476</v>
       </c>
-      <c r="G24" s="7">
-        <v>750</v>
-      </c>
-      <c r="H24" s="7">
-        <v>18</v>
+      <c r="L24" s="7">
+        <v>1137.10496244</v>
+      </c>
+      <c r="M24" s="7">
+        <v>1145.19467003</v>
+      </c>
+      <c r="N24" s="7">
+        <v>543.99735204</v>
+      </c>
+      <c r="O24" s="7">
+        <v>1.80390036</v>
+      </c>
+      <c r="P24" s="7">
+        <v>2.25904157</v>
+      </c>
+      <c r="Q24" s="7">
+        <v>5.15081216</v>
+      </c>
+      <c r="R24" s="7">
+        <v>56905.33333333</v>
+      </c>
+      <c r="S24" s="7">
+        <v>3.09550355</v>
       </c>
     </row>
     <row r="25">
@@ -1098,25 +1967,58 @@
         </is>
       </c>
       <c r="B25" s="7">
+        <v>1802593</v>
+      </c>
+      <c r="C25" s="7">
+        <v>663.51808303</v>
+      </c>
+      <c r="D25" s="7">
+        <v>29781.07084459</v>
+      </c>
+      <c r="E25" s="7">
+        <v>432327</v>
+      </c>
+      <c r="F25" s="7">
         <v>55.33914769</v>
       </c>
-      <c r="C25" s="7">
+      <c r="G25" s="7">
+        <v>5737.25018756</v>
+      </c>
+      <c r="H25" s="7">
+        <v>142986</v>
+      </c>
+      <c r="I25" s="7">
+        <v>196072</v>
+      </c>
+      <c r="J25" s="7">
         <v>93.90137844</v>
       </c>
-      <c r="D25" s="7">
-        <v>5737.25018756</v>
-      </c>
-      <c r="E25" s="7">
-        <v>29781.07084459</v>
-      </c>
-      <c r="F25" s="7">
+      <c r="K25" s="7">
         <v>22.41620607</v>
       </c>
-      <c r="G25" s="7">
-        <v>1802593</v>
-      </c>
-      <c r="H25" s="7">
-        <v>414488</v>
+      <c r="L25" s="7">
+        <v>6083.23257082</v>
+      </c>
+      <c r="M25" s="7">
+        <v>1742.17316816</v>
+      </c>
+      <c r="N25" s="7">
+        <v>2827.48085763</v>
+      </c>
+      <c r="O25" s="7">
+        <v>35.87152778</v>
+      </c>
+      <c r="P25" s="7">
+        <v>59.77891654</v>
+      </c>
+      <c r="Q25" s="7">
+        <v>60</v>
+      </c>
+      <c r="R25" s="7">
+        <v>67311.33333333</v>
+      </c>
+      <c r="S25" s="7">
+        <v>55.33914769</v>
       </c>
     </row>
     <row r="26">
@@ -1126,25 +2028,58 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <v>3.55653492</v>
+        <v>1320050</v>
       </c>
       <c r="C26" s="7">
+        <v>4.30322252</v>
+      </c>
+      <c r="D26" s="7">
+        <v>12805.89226846</v>
+      </c>
+      <c r="E26" s="7">
+        <v>216170</v>
+      </c>
+      <c r="F26" s="7">
+        <v>3.55457963</v>
+      </c>
+      <c r="G26" s="7">
+        <v>1665.73474081</v>
+      </c>
+      <c r="H26" s="7">
+        <v>90720</v>
+      </c>
+      <c r="I26" s="7">
+        <v>89642</v>
+      </c>
+      <c r="J26" s="7">
         <v>81.17522855</v>
       </c>
-      <c r="D26" s="7">
-        <v>1665.73474081</v>
-      </c>
-      <c r="E26" s="7">
-        <v>26277.879379265</v>
-      </c>
-      <c r="F26" s="7">
-        <v>3.521428325</v>
-      </c>
-      <c r="G26" s="7">
-        <v>1317271.5</v>
-      </c>
-      <c r="H26" s="7">
-        <v>215806</v>
+      <c r="K26" s="7">
+        <v>3.521428185</v>
+      </c>
+      <c r="L26" s="7">
+        <v>1359.02495043</v>
+      </c>
+      <c r="M26" s="7">
+        <v>1329.25056522</v>
+      </c>
+      <c r="N26" s="7">
+        <v>739.2142845000001</v>
+      </c>
+      <c r="O26" s="7">
+        <v>2.38235867</v>
+      </c>
+      <c r="P26" s="7">
+        <v>3.85279436</v>
+      </c>
+      <c r="Q26" s="7">
+        <v>6.25351215</v>
+      </c>
+      <c r="R26" s="7">
+        <v>61884.33333333</v>
+      </c>
+      <c r="S26" s="7">
+        <v>3.55457963</v>
       </c>
     </row>
     <row r="27">
@@ -1154,25 +2089,58 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <v>1018.79480301</v>
+        <v>115976571</v>
       </c>
       <c r="C27" s="7">
+        <v>2279.61164604</v>
+      </c>
+      <c r="D27" s="7">
+        <v>468598.0907629401</v>
+      </c>
+      <c r="E27" s="7">
+        <v>19323691</v>
+      </c>
+      <c r="F27" s="7">
+        <v>1022.1812629</v>
+      </c>
+      <c r="G27" s="7">
+        <v>20987.80516466</v>
+      </c>
+      <c r="H27" s="7">
+        <v>8297179</v>
+      </c>
+      <c r="I27" s="7">
+        <v>8768006</v>
+      </c>
+      <c r="J27" s="7">
         <v>8458.435797029999</v>
       </c>
-      <c r="D27" s="7">
-        <v>20987.80516466</v>
-      </c>
-      <c r="E27" s="7">
-        <v>206801.13317019</v>
-      </c>
-      <c r="F27" s="7">
-        <v>56.0709143</v>
-      </c>
-      <c r="G27" s="7">
-        <v>114475576</v>
-      </c>
-      <c r="H27" s="7">
-        <v>18891363</v>
+      <c r="K27" s="7">
+        <v>56.07091402</v>
+      </c>
+      <c r="L27" s="7">
+        <v>22102.09549848</v>
+      </c>
+      <c r="M27" s="7">
+        <v>13753.06732667</v>
+      </c>
+      <c r="N27" s="7">
+        <v>9545.68023881</v>
+      </c>
+      <c r="O27" s="7">
+        <v>501.9986266099999</v>
+      </c>
+      <c r="P27" s="7">
+        <v>1288.24709375</v>
+      </c>
+      <c r="Q27" s="7">
+        <v>1712.61649148</v>
+      </c>
+      <c r="R27" s="7">
+        <v>2306080.66666666</v>
+      </c>
+      <c r="S27" s="7">
+        <v>1022.1812629</v>
       </c>
     </row>
     <row r="28">
@@ -1182,25 +2150,58 @@
         </is>
       </c>
       <c r="B28" s="7">
+        <v>-1801843</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-752.9824235999999</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-29356.55252677</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-432309</v>
+      </c>
+      <c r="F28" s="7">
         <v>-52.24364414</v>
       </c>
-      <c r="C28" s="7">
+      <c r="G28" s="7">
+        <v>-4307.49954915</v>
+      </c>
+      <c r="H28" s="7">
+        <v>-142890</v>
+      </c>
+      <c r="I28" s="7">
+        <v>-196060</v>
+      </c>
+      <c r="J28" s="7">
         <v>-53.73913381000001</v>
       </c>
-      <c r="D28" s="7">
-        <v>-4307.49954915</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-27887.43978494</v>
-      </c>
-      <c r="F28" s="7">
+      <c r="K28" s="7">
         <v>-19.08607131</v>
       </c>
-      <c r="G28" s="7">
-        <v>-1801843</v>
-      </c>
-      <c r="H28" s="7">
-        <v>-414470</v>
+      <c r="L28" s="7">
+        <v>-4946.127608379999</v>
+      </c>
+      <c r="M28" s="7">
+        <v>-596.9784981299999</v>
+      </c>
+      <c r="N28" s="7">
+        <v>-2283.48350559</v>
+      </c>
+      <c r="O28" s="7">
+        <v>-34.06762742</v>
+      </c>
+      <c r="P28" s="7">
+        <v>-57.51987497</v>
+      </c>
+      <c r="Q28" s="7">
+        <v>-54.84918784</v>
+      </c>
+      <c r="R28" s="7">
+        <v>-10405.99999999999</v>
+      </c>
+      <c r="S28" s="7">
+        <v>-52.24364414</v>
       </c>
     </row>
     <row r="29">
@@ -1210,1936 +2211,4279 @@
         </is>
       </c>
       <c r="B29" s="2">
+        <v>111</v>
+      </c>
+      <c r="C29" s="2">
+        <v>36</v>
+      </c>
+      <c r="D29" s="2">
+        <v>36</v>
+      </c>
+      <c r="E29" s="2">
+        <v>111</v>
+      </c>
+      <c r="F29" s="2">
+        <v>111</v>
+      </c>
+      <c r="G29" s="2">
+        <v>10</v>
+      </c>
+      <c r="H29" s="2">
+        <v>111</v>
+      </c>
+      <c r="I29" s="2">
+        <v>111</v>
+      </c>
+      <c r="J29" s="2">
         <v>110</v>
       </c>
-      <c r="C29" s="2">
-        <v>110</v>
-      </c>
-      <c r="D29" s="2">
+      <c r="K29" s="2">
         <v>10</v>
       </c>
-      <c r="E29" s="2">
+      <c r="L29" s="2">
         <v>10</v>
       </c>
-      <c r="F29" s="2">
+      <c r="M29" s="2">
         <v>10</v>
       </c>
-      <c r="G29" s="2">
-        <v>110</v>
-      </c>
-      <c r="H29" s="2">
-        <v>110</v>
+      <c r="N29" s="2">
+        <v>10</v>
+      </c>
+      <c r="O29" s="2">
+        <v>111</v>
+      </c>
+      <c r="P29" s="2">
+        <v>111</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>111</v>
+      </c>
+      <c r="R29" s="2">
+        <v>37</v>
+      </c>
+      <c r="S29" s="2">
+        <v>111</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8">
         <v>42339</v>
       </c>
-      <c r="D30" s="1">
+      <c r="G30" s="1">
         <v>1429.75063841</v>
       </c>
-      <c r="E30" s="1">
-        <v>21777.20252672</v>
+      <c r="L30" s="1">
+        <v>1204.64911853</v>
+      </c>
+      <c r="M30" s="1">
+        <v>1150.72943267</v>
+      </c>
+      <c r="N30" s="1">
+        <v>543.99735204</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8">
         <v>42705</v>
       </c>
-      <c r="B31" s="9">
+      <c r="B31" s="1">
+        <v>1506134</v>
+      </c>
+      <c r="C31" s="1">
+        <v>18.23581245</v>
+      </c>
+      <c r="D31" s="1">
+        <v>25748.45233567</v>
+      </c>
+      <c r="E31" s="1">
+        <v>226020</v>
+      </c>
+      <c r="F31" s="9">
         <v>3.21434604</v>
       </c>
-      <c r="C31" s="1">
+      <c r="G31" s="1">
+        <v>1569.69727502</v>
+      </c>
+      <c r="H31" s="1">
+        <v>128897</v>
+      </c>
+      <c r="I31" s="1">
+        <v>94323</v>
+      </c>
+      <c r="J31" s="1">
         <v>79.61206620999999</v>
       </c>
-      <c r="D31" s="1">
-        <v>1569.69727502</v>
-      </c>
-      <c r="E31" s="1">
-        <v>25748.45233567</v>
-      </c>
-      <c r="F31" s="1">
+      <c r="K31" s="1">
         <v>3.42985924</v>
       </c>
-      <c r="G31" s="1">
-        <v>1506134</v>
-      </c>
-      <c r="H31" s="1">
-        <v>226020</v>
+      <c r="L31" s="1">
+        <v>1232.42107204</v>
+      </c>
+      <c r="M31" s="1">
+        <v>1419.33856364</v>
+      </c>
+      <c r="N31" s="1">
+        <v>677.27493788</v>
+      </c>
+      <c r="O31" s="1">
+        <v>2.46833635</v>
+      </c>
+      <c r="P31" s="1">
+        <v>2.50547552</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>6.09538271</v>
+      </c>
+      <c r="R31" s="1">
+        <v>57010.33333333</v>
+      </c>
+      <c r="S31" s="9">
+        <v>3.21434604</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8">
         <v>42736</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="1">
+        <v>1480479</v>
+      </c>
+      <c r="E32" s="1">
+        <v>316805</v>
+      </c>
+      <c r="F32" s="9">
         <v>3.51735288</v>
       </c>
-      <c r="C32" s="1">
+      <c r="H32" s="1">
+        <v>84504</v>
+      </c>
+      <c r="I32" s="1">
+        <v>80062</v>
+      </c>
+      <c r="J32" s="1">
         <v>81.76737245</v>
       </c>
-      <c r="G32" s="1">
-        <v>1480479</v>
-      </c>
-      <c r="H32" s="1">
-        <v>316805</v>
+      <c r="O32" s="1">
+        <v>2.31418293</v>
+      </c>
+      <c r="P32" s="1">
+        <v>3.06391824</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>6.2373516</v>
+      </c>
+      <c r="S32" s="9">
+        <v>3.51735288</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8">
         <v>42767</v>
       </c>
-      <c r="B33" s="9">
+      <c r="B33" s="1">
+        <v>1361010</v>
+      </c>
+      <c r="E33" s="1">
+        <v>268993</v>
+      </c>
+      <c r="F33" s="9">
         <v>3.42351625</v>
       </c>
-      <c r="C33" s="1">
+      <c r="H33" s="1">
+        <v>85058</v>
+      </c>
+      <c r="I33" s="1">
+        <v>75905</v>
+      </c>
+      <c r="J33" s="1">
         <v>88.02774565999999</v>
       </c>
-      <c r="G33" s="1">
-        <v>1361010</v>
-      </c>
-      <c r="H33" s="1">
-        <v>268993</v>
+      <c r="O33" s="1">
+        <v>2.16703567</v>
+      </c>
+      <c r="P33" s="1">
+        <v>3.83158345</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>5.94482639</v>
+      </c>
+      <c r="S33" s="9">
+        <v>3.42351625</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8">
         <v>42795</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="1">
+        <v>1480161</v>
+      </c>
+      <c r="C34" s="1">
+        <v>19.24716717</v>
+      </c>
+      <c r="D34" s="1">
+        <v>6724.5678785</v>
+      </c>
+      <c r="E34" s="1">
+        <v>264711</v>
+      </c>
+      <c r="F34" s="9">
         <v>3.15055147</v>
       </c>
-      <c r="C34" s="1">
+      <c r="H34" s="1">
+        <v>105372</v>
+      </c>
+      <c r="I34" s="1">
+        <v>85299</v>
+      </c>
+      <c r="J34" s="1">
         <v>84.67200801</v>
       </c>
-      <c r="G34" s="1">
-        <v>1480161</v>
-      </c>
-      <c r="H34" s="1">
-        <v>264711</v>
+      <c r="O34" s="1">
+        <v>2.16005147</v>
+      </c>
+      <c r="P34" s="1">
+        <v>2.50604396</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>6.25351215</v>
+      </c>
+      <c r="R34" s="1">
+        <v>56905.33333333</v>
+      </c>
+      <c r="S34" s="9">
+        <v>3.15055147</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8">
         <v>42826</v>
       </c>
-      <c r="B35" s="9">
+      <c r="B35" s="1">
+        <v>1470750</v>
+      </c>
+      <c r="E35" s="1">
+        <v>252135</v>
+      </c>
+      <c r="F35" s="9">
         <v>3.28076748</v>
       </c>
-      <c r="C35" s="1">
+      <c r="H35" s="1">
+        <v>94550</v>
+      </c>
+      <c r="I35" s="1">
+        <v>109303</v>
+      </c>
+      <c r="J35" s="1">
         <v>85.06826334</v>
       </c>
-      <c r="G35" s="1">
-        <v>1470750</v>
-      </c>
-      <c r="H35" s="1">
-        <v>252135</v>
+      <c r="O35" s="1">
+        <v>2.17649405</v>
+      </c>
+      <c r="P35" s="1">
+        <v>2.52860288</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>6.10184324</v>
+      </c>
+      <c r="S35" s="9">
+        <v>3.28076748</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8">
         <v>42856</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="1">
+        <v>1363897</v>
+      </c>
+      <c r="E36" s="1">
+        <v>232361</v>
+      </c>
+      <c r="F36" s="9">
         <v>3.54908271</v>
       </c>
-      <c r="C36" s="1">
+      <c r="H36" s="1">
+        <v>90335</v>
+      </c>
+      <c r="I36" s="1">
+        <v>172822</v>
+      </c>
+      <c r="J36" s="1">
         <v>82.27882296999999</v>
       </c>
-      <c r="G36" s="1">
-        <v>1363897</v>
-      </c>
-      <c r="H36" s="1">
-        <v>232361</v>
+      <c r="O36" s="1">
+        <v>2.29529616</v>
+      </c>
+      <c r="P36" s="1">
+        <v>2.6136063</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>5.80073653</v>
+      </c>
+      <c r="S36" s="9">
+        <v>3.54908271</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8">
         <v>42887</v>
       </c>
-      <c r="B37" s="9">
+      <c r="B37" s="1">
+        <v>1387601</v>
+      </c>
+      <c r="C37" s="1">
+        <v>9.25653067</v>
+      </c>
+      <c r="D37" s="1">
+        <v>13404.76334795</v>
+      </c>
+      <c r="E37" s="1">
+        <v>218118</v>
+      </c>
+      <c r="F37" s="9">
         <v>3.627402</v>
       </c>
-      <c r="C37" s="1">
+      <c r="H37" s="1">
+        <v>102776</v>
+      </c>
+      <c r="I37" s="1">
+        <v>136478</v>
+      </c>
+      <c r="J37" s="1">
         <v>83.7548828</v>
       </c>
-      <c r="G37" s="1">
-        <v>1387601</v>
-      </c>
-      <c r="H37" s="1">
-        <v>218118</v>
+      <c r="O37" s="1">
+        <v>2.36688536</v>
+      </c>
+      <c r="P37" s="1">
+        <v>2.77891052</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>6.56343555</v>
+      </c>
+      <c r="R37" s="1">
+        <v>57104.66666667</v>
+      </c>
+      <c r="S37" s="9">
+        <v>3.627402</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8">
         <v>42917</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="1">
+        <v>1632135</v>
+      </c>
+      <c r="E38" s="1">
+        <v>349654</v>
+      </c>
+      <c r="F38" s="9">
         <v>3.50191372</v>
       </c>
-      <c r="C38" s="1">
+      <c r="H38" s="1">
+        <v>87138</v>
+      </c>
+      <c r="I38" s="1">
+        <v>97125</v>
+      </c>
+      <c r="J38" s="1">
         <v>91.53710721</v>
       </c>
-      <c r="G38" s="1">
-        <v>1632135</v>
-      </c>
-      <c r="H38" s="1">
-        <v>349654</v>
+      <c r="O38" s="1">
+        <v>2.39704881</v>
+      </c>
+      <c r="P38" s="1">
+        <v>3.04501951</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>6.17781327</v>
+      </c>
+      <c r="S38" s="9">
+        <v>3.50191372</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8">
         <v>42948</v>
       </c>
-      <c r="B39" s="9">
+      <c r="B39" s="1">
+        <v>1559283</v>
+      </c>
+      <c r="E39" s="1">
+        <v>357287</v>
+      </c>
+      <c r="F39" s="9">
         <v>3.53168791</v>
       </c>
-      <c r="C39" s="1">
+      <c r="H39" s="1">
+        <v>91135</v>
+      </c>
+      <c r="I39" s="1">
+        <v>91551</v>
+      </c>
+      <c r="J39" s="1">
         <v>89.35634524</v>
       </c>
-      <c r="G39" s="1">
-        <v>1559283</v>
-      </c>
-      <c r="H39" s="1">
-        <v>357287</v>
+      <c r="O39" s="1">
+        <v>2.39046093</v>
+      </c>
+      <c r="P39" s="1">
+        <v>3.43346716</v>
+      </c>
+      <c r="Q39" s="1">
+        <v>6.14766759</v>
+      </c>
+      <c r="S39" s="9">
+        <v>3.53168791</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8">
         <v>42979</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="1">
+        <v>1320050</v>
+      </c>
+      <c r="C40" s="1">
+        <v>4.98809443</v>
+      </c>
+      <c r="D40" s="1">
+        <v>20345.77697974</v>
+      </c>
+      <c r="E40" s="1">
+        <v>226978</v>
+      </c>
+      <c r="F40" s="9">
         <v>3.3320192</v>
       </c>
-      <c r="C40" s="1">
+      <c r="H40" s="1">
+        <v>90837</v>
+      </c>
+      <c r="I40" s="1">
+        <v>102262</v>
+      </c>
+      <c r="J40" s="1">
         <v>84.33686469</v>
       </c>
-      <c r="G40" s="1">
-        <v>1320050</v>
-      </c>
-      <c r="H40" s="1">
-        <v>226978</v>
+      <c r="O40" s="1">
+        <v>2.30039453</v>
+      </c>
+      <c r="P40" s="1">
+        <v>2.75410352</v>
+      </c>
+      <c r="Q40" s="1">
+        <v>5.74483001</v>
+      </c>
+      <c r="R40" s="1">
+        <v>57685</v>
+      </c>
+      <c r="S40" s="9">
+        <v>3.3320192</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8">
         <v>43009</v>
       </c>
-      <c r="B41" s="9">
+      <c r="B41" s="1">
+        <v>1402299</v>
+      </c>
+      <c r="E41" s="1">
+        <v>245755</v>
+      </c>
+      <c r="F41" s="9">
         <v>3.24726355</v>
       </c>
-      <c r="C41" s="1">
+      <c r="H41" s="1">
+        <v>96015</v>
+      </c>
+      <c r="I41" s="1">
+        <v>120100</v>
+      </c>
+      <c r="J41" s="1">
         <v>83.12943322</v>
       </c>
-      <c r="G41" s="1">
-        <v>1402299</v>
-      </c>
-      <c r="H41" s="1">
-        <v>245755</v>
+      <c r="O41" s="1">
+        <v>2.17894232</v>
+      </c>
+      <c r="P41" s="1">
+        <v>2.75322838</v>
+      </c>
+      <c r="Q41" s="1">
+        <v>5.15081216</v>
+      </c>
+      <c r="S41" s="9">
+        <v>3.24726355</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8">
         <v>43040</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="1">
+        <v>1397330</v>
+      </c>
+      <c r="E42" s="1">
+        <v>251096</v>
+      </c>
+      <c r="F42" s="9">
         <v>3.09550355</v>
       </c>
-      <c r="C42" s="1">
+      <c r="H42" s="1">
+        <v>105404</v>
+      </c>
+      <c r="I42" s="1">
+        <v>86432</v>
+      </c>
+      <c r="J42" s="1">
         <v>85.17217875999999</v>
       </c>
-      <c r="G42" s="1">
-        <v>1397330</v>
-      </c>
-      <c r="H42" s="1">
-        <v>251096</v>
+      <c r="O42" s="1">
+        <v>2.13505275</v>
+      </c>
+      <c r="P42" s="1">
+        <v>2.25904157</v>
+      </c>
+      <c r="Q42" s="1">
+        <v>6.00874076</v>
+      </c>
+      <c r="S42" s="9">
+        <v>3.09550355</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8">
         <v>43070</v>
       </c>
-      <c r="B43" s="9">
+      <c r="B43" s="1">
+        <v>1569616</v>
+      </c>
+      <c r="C43" s="1">
+        <v>4.11230187</v>
+      </c>
+      <c r="D43" s="1">
+        <v>26807.30642286</v>
+      </c>
+      <c r="E43" s="1">
+        <v>244241</v>
+      </c>
+      <c r="F43" s="9">
         <v>3.2243555</v>
       </c>
-      <c r="C43" s="1">
+      <c r="G43" s="1">
+        <v>1538.62844341</v>
+      </c>
+      <c r="H43" s="1">
+        <v>135260</v>
+      </c>
+      <c r="I43" s="1">
+        <v>114738</v>
+      </c>
+      <c r="J43" s="1">
         <v>79.64258954</v>
       </c>
-      <c r="D43" s="1">
-        <v>1538.62844341</v>
-      </c>
-      <c r="E43" s="1">
-        <v>26807.30642286</v>
-      </c>
-      <c r="F43" s="1">
+      <c r="K43" s="1">
         <v>3.37586597</v>
       </c>
-      <c r="G43" s="1">
-        <v>1569616</v>
-      </c>
-      <c r="H43" s="1">
-        <v>244241</v>
+      <c r="L43" s="1">
+        <v>1201.66265846</v>
+      </c>
+      <c r="M43" s="1">
+        <v>1215.02325864</v>
+      </c>
+      <c r="N43" s="1">
+        <v>716.5546885</v>
+      </c>
+      <c r="O43" s="1">
+        <v>2.51352541</v>
+      </c>
+      <c r="P43" s="1">
+        <v>2.46171375</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>5.65775098</v>
+      </c>
+      <c r="R43" s="1">
+        <v>58865.66666667</v>
+      </c>
+      <c r="S43" s="9">
+        <v>3.2243555</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8">
         <v>43101</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B44" s="1">
+        <v>1563359</v>
+      </c>
+      <c r="E44" s="1">
+        <v>291208</v>
+      </c>
+      <c r="F44" s="9">
         <v>3.3733835</v>
       </c>
-      <c r="C44" s="1">
+      <c r="H44" s="1">
+        <v>86833</v>
+      </c>
+      <c r="I44" s="1">
+        <v>108067</v>
+      </c>
+      <c r="J44" s="1">
         <v>83.4206083</v>
       </c>
-      <c r="G44" s="1">
-        <v>1563359</v>
-      </c>
-      <c r="H44" s="1">
-        <v>291208</v>
+      <c r="O44" s="1">
+        <v>2.37462726</v>
+      </c>
+      <c r="P44" s="1">
+        <v>2.68143642</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>5.70421911</v>
+      </c>
+      <c r="S44" s="9">
+        <v>3.3733835</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8">
         <v>43132</v>
       </c>
-      <c r="B45" s="9">
+      <c r="B45" s="1">
+        <v>1491970</v>
+      </c>
+      <c r="E45" s="1">
+        <v>366616</v>
+      </c>
+      <c r="F45" s="9">
         <v>3.34971865</v>
       </c>
-      <c r="C45" s="1">
+      <c r="H45" s="1">
+        <v>85212</v>
+      </c>
+      <c r="I45" s="1">
+        <v>81797</v>
+      </c>
+      <c r="J45" s="1">
         <v>87.99437558</v>
       </c>
-      <c r="G45" s="1">
-        <v>1491970</v>
-      </c>
-      <c r="H45" s="1">
-        <v>366616</v>
+      <c r="O45" s="1">
+        <v>2.24626552</v>
+      </c>
+      <c r="P45" s="1">
+        <v>3.38499693</v>
+      </c>
+      <c r="Q45" s="1">
+        <v>5.89687342</v>
+      </c>
+      <c r="S45" s="9">
+        <v>3.34971865</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8">
         <v>43160</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="1">
+        <v>1584406</v>
+      </c>
+      <c r="C46" s="1">
+        <v>2.12980146</v>
+      </c>
+      <c r="D46" s="1">
+        <v>6867.78782354</v>
+      </c>
+      <c r="E46" s="1">
+        <v>274879</v>
+      </c>
+      <c r="F46" s="9">
         <v>3.20436545</v>
       </c>
-      <c r="C46" s="1">
+      <c r="H46" s="1">
+        <v>109897</v>
+      </c>
+      <c r="I46" s="1">
+        <v>105560</v>
+      </c>
+      <c r="J46" s="1">
         <v>87.20196257000001</v>
       </c>
-      <c r="G46" s="1">
-        <v>1584406</v>
-      </c>
-      <c r="H46" s="1">
-        <v>274879</v>
+      <c r="O46" s="1">
+        <v>2.14892155</v>
+      </c>
+      <c r="P46" s="1">
+        <v>2.86383821</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>5.73386345</v>
+      </c>
+      <c r="R46" s="1">
+        <v>58611</v>
+      </c>
+      <c r="S46" s="9">
+        <v>3.20436545</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8">
         <v>43191</v>
       </c>
-      <c r="B47" s="9">
+      <c r="B47" s="1">
+        <v>1544248</v>
+      </c>
+      <c r="E47" s="1">
+        <v>291119</v>
+      </c>
+      <c r="F47" s="9">
         <v>3.20647151</v>
       </c>
-      <c r="C47" s="1">
+      <c r="H47" s="1">
+        <v>98351</v>
+      </c>
+      <c r="I47" s="1">
+        <v>122229</v>
+      </c>
+      <c r="J47" s="1">
         <v>85.23803395</v>
       </c>
-      <c r="G47" s="1">
-        <v>1544248</v>
-      </c>
-      <c r="H47" s="1">
-        <v>291119</v>
+      <c r="O47" s="1">
+        <v>2.27141087</v>
+      </c>
+      <c r="P47" s="1">
+        <v>2.38793669</v>
+      </c>
+      <c r="Q47" s="1">
+        <v>5.65952028</v>
+      </c>
+      <c r="S47" s="9">
+        <v>3.20647151</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8">
         <v>43221</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B48" s="1">
+        <v>1470891</v>
+      </c>
+      <c r="E48" s="1">
+        <v>264802</v>
+      </c>
+      <c r="F48" s="9">
         <v>3.48318485</v>
       </c>
-      <c r="C48" s="1">
+      <c r="H48" s="1">
+        <v>91244</v>
+      </c>
+      <c r="I48" s="1">
+        <v>196072</v>
+      </c>
+      <c r="J48" s="1">
         <v>82.56325905999999</v>
       </c>
-      <c r="G48" s="1">
-        <v>1470891</v>
-      </c>
-      <c r="H48" s="1">
-        <v>264802</v>
+      <c r="O48" s="1">
+        <v>2.3855538</v>
+      </c>
+      <c r="P48" s="1">
+        <v>2.50585501</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>5.46632661</v>
+      </c>
+      <c r="S48" s="9">
+        <v>3.48318485</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8">
         <v>43252</v>
       </c>
-      <c r="B49" s="9">
+      <c r="B49" s="1">
+        <v>1544679</v>
+      </c>
+      <c r="C49" s="1">
+        <v>0.42493511</v>
+      </c>
+      <c r="D49" s="1">
+        <v>13461.72489445</v>
+      </c>
+      <c r="E49" s="1">
+        <v>242118</v>
+      </c>
+      <c r="F49" s="9">
         <v>3.55849021</v>
       </c>
-      <c r="C49" s="1">
+      <c r="H49" s="1">
+        <v>113049</v>
+      </c>
+      <c r="I49" s="1">
+        <v>154945</v>
+      </c>
+      <c r="J49" s="1">
         <v>85.46062713000001</v>
       </c>
-      <c r="G49" s="1">
-        <v>1544679</v>
-      </c>
-      <c r="H49" s="1">
-        <v>242118</v>
+      <c r="O49" s="1">
+        <v>2.41409883</v>
+      </c>
+      <c r="P49" s="1">
+        <v>2.68665172</v>
+      </c>
+      <c r="Q49" s="1">
+        <v>6.24669595</v>
+      </c>
+      <c r="R49" s="1">
+        <v>60580.33333333</v>
+      </c>
+      <c r="S49" s="9">
+        <v>3.55849021</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8">
         <v>43282</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B50" s="1">
+        <v>1732896</v>
+      </c>
+      <c r="E50" s="1">
+        <v>361019</v>
+      </c>
+      <c r="F50" s="9">
         <v>3.40593015</v>
       </c>
-      <c r="C50" s="1">
+      <c r="H50" s="1">
+        <v>94611</v>
+      </c>
+      <c r="I50" s="1">
+        <v>117798</v>
+      </c>
+      <c r="J50" s="1">
         <v>92.38596414</v>
       </c>
-      <c r="G50" s="1">
-        <v>1732896</v>
-      </c>
-      <c r="H50" s="1">
-        <v>361019</v>
+      <c r="O50" s="1">
+        <v>2.39808801</v>
+      </c>
+      <c r="P50" s="1">
+        <v>3.12626421</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>5.51480944</v>
+      </c>
+      <c r="S50" s="9">
+        <v>3.40593015</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8">
         <v>43313</v>
       </c>
-      <c r="B51" s="9">
+      <c r="B51" s="1">
+        <v>1683122</v>
+      </c>
+      <c r="E51" s="1">
+        <v>380108</v>
+      </c>
+      <c r="F51" s="9">
         <v>3.48967601</v>
       </c>
-      <c r="C51" s="1">
+      <c r="H51" s="1">
+        <v>103490</v>
+      </c>
+      <c r="I51" s="1">
+        <v>100744</v>
+      </c>
+      <c r="J51" s="1">
         <v>91.52662436</v>
       </c>
-      <c r="G51" s="1">
-        <v>1683122</v>
-      </c>
-      <c r="H51" s="1">
-        <v>380108</v>
+      <c r="O51" s="1">
+        <v>2.33249002</v>
+      </c>
+      <c r="P51" s="1">
+        <v>3.5416245</v>
+      </c>
+      <c r="Q51" s="1">
+        <v>6.03306431</v>
+      </c>
+      <c r="S51" s="9">
+        <v>3.48967601</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8">
         <v>43344</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B52" s="1">
+        <v>1415149</v>
+      </c>
+      <c r="C52" s="1">
+        <v>1.30145167</v>
+      </c>
+      <c r="D52" s="1">
+        <v>20610.56743432</v>
+      </c>
+      <c r="E52" s="1">
+        <v>239824</v>
+      </c>
+      <c r="F52" s="9">
         <v>3.26595709</v>
       </c>
-      <c r="C52" s="1">
+      <c r="H52" s="1">
+        <v>106880</v>
+      </c>
+      <c r="I52" s="1">
+        <v>102251</v>
+      </c>
+      <c r="J52" s="1">
         <v>85.33643060999999</v>
       </c>
-      <c r="G52" s="1">
-        <v>1415149</v>
-      </c>
-      <c r="H52" s="1">
-        <v>239824</v>
+      <c r="O52" s="1">
+        <v>2.18802886</v>
+      </c>
+      <c r="P52" s="1">
+        <v>2.8225389</v>
+      </c>
+      <c r="Q52" s="1">
+        <v>5.6078913</v>
+      </c>
+      <c r="R52" s="1">
+        <v>60360.33333333</v>
+      </c>
+      <c r="S52" s="9">
+        <v>3.26595709</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8">
         <v>43374</v>
       </c>
-      <c r="B53" s="9">
+      <c r="B53" s="1">
+        <v>1467380</v>
+      </c>
+      <c r="E53" s="1">
+        <v>247664</v>
+      </c>
+      <c r="F53" s="9">
         <v>3.20025075</v>
       </c>
-      <c r="C53" s="1">
+      <c r="H53" s="1">
+        <v>103676</v>
+      </c>
+      <c r="I53" s="1">
+        <v>114000</v>
+      </c>
+      <c r="J53" s="1">
         <v>86.36776498</v>
       </c>
-      <c r="G53" s="1">
-        <v>1467380</v>
-      </c>
-      <c r="H53" s="1">
-        <v>247664</v>
+      <c r="O53" s="1">
+        <v>2.14257545</v>
+      </c>
+      <c r="P53" s="1">
+        <v>2.7725963</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>5.34981005</v>
+      </c>
+      <c r="S53" s="9">
+        <v>3.20025075</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8">
         <v>43405</v>
       </c>
-      <c r="B54" s="9">
+      <c r="B54" s="1">
+        <v>1406985</v>
+      </c>
+      <c r="E54" s="1">
+        <v>220053</v>
+      </c>
+      <c r="F54" s="9">
         <v>3.14124728</v>
       </c>
-      <c r="C54" s="1">
+      <c r="H54" s="1">
+        <v>117793</v>
+      </c>
+      <c r="I54" s="1">
+        <v>121319</v>
+      </c>
+      <c r="J54" s="1">
         <v>84.94951897</v>
       </c>
-      <c r="G54" s="1">
-        <v>1406985</v>
-      </c>
-      <c r="H54" s="1">
-        <v>220053</v>
+      <c r="O54" s="1">
+        <v>2.11471188</v>
+      </c>
+      <c r="P54" s="1">
+        <v>2.52832431</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>5.16236631</v>
+      </c>
+      <c r="S54" s="9">
+        <v>3.14124728</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="8">
         <v>43435</v>
       </c>
-      <c r="B55" s="9">
+      <c r="B55" s="1">
+        <v>1603217</v>
+      </c>
+      <c r="C55" s="1">
+        <v>0.50147446</v>
+      </c>
+      <c r="D55" s="1">
+        <v>26941.73821809</v>
+      </c>
+      <c r="E55" s="1">
+        <v>238194</v>
+      </c>
+      <c r="F55" s="9">
         <v>3.22542619</v>
       </c>
-      <c r="C55" s="1">
+      <c r="G55" s="1">
+        <v>1456.21248964</v>
+      </c>
+      <c r="H55" s="1">
+        <v>142986</v>
+      </c>
+      <c r="I55" s="1">
+        <v>117495</v>
+      </c>
+      <c r="J55" s="1">
         <v>80.74555579</v>
       </c>
-      <c r="D55" s="1">
-        <v>1456.21248964</v>
-      </c>
-      <c r="E55" s="1">
-        <v>26941.73821809</v>
-      </c>
-      <c r="F55" s="1">
+      <c r="K55" s="1">
         <v>3.33013476</v>
       </c>
-      <c r="G55" s="1">
-        <v>1603217</v>
-      </c>
-      <c r="H55" s="1">
-        <v>238194</v>
+      <c r="L55" s="1">
+        <v>1145.97247311</v>
+      </c>
+      <c r="M55" s="1">
+        <v>1212.0447742</v>
+      </c>
+      <c r="N55" s="1">
+        <v>656.93873013</v>
+      </c>
+      <c r="O55" s="1">
+        <v>2.49344802</v>
+      </c>
+      <c r="P55" s="1">
+        <v>2.58639264</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>5.66983868</v>
+      </c>
+      <c r="R55" s="1">
+        <v>60612</v>
+      </c>
+      <c r="S55" s="9">
+        <v>3.22542619</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8">
         <v>43466</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B56" s="1">
+        <v>1624593</v>
+      </c>
+      <c r="E56" s="1">
+        <v>320581</v>
+      </c>
+      <c r="F56" s="9">
         <v>3.42031923</v>
       </c>
-      <c r="C56" s="1">
+      <c r="H56" s="1">
+        <v>88293</v>
+      </c>
+      <c r="I56" s="1">
+        <v>104562</v>
+      </c>
+      <c r="J56" s="1">
         <v>84.71312863</v>
       </c>
-      <c r="G56" s="1">
-        <v>1624593</v>
-      </c>
-      <c r="H56" s="1">
-        <v>320581</v>
+      <c r="O56" s="1">
+        <v>2.34878503</v>
+      </c>
+      <c r="P56" s="1">
+        <v>3.02234335</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>5.82711477</v>
+      </c>
+      <c r="S56" s="9">
+        <v>3.42031923</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8">
         <v>43497</v>
       </c>
-      <c r="B57" s="9">
+      <c r="B57" s="1">
+        <v>1499051</v>
+      </c>
+      <c r="E57" s="1">
+        <v>339550</v>
+      </c>
+      <c r="F57" s="9">
         <v>3.46075053</v>
       </c>
-      <c r="C57" s="1">
+      <c r="H57" s="1">
+        <v>88706</v>
+      </c>
+      <c r="I57" s="1">
+        <v>88926</v>
+      </c>
+      <c r="J57" s="1">
         <v>88.48043393</v>
       </c>
-      <c r="G57" s="1">
-        <v>1499051</v>
-      </c>
-      <c r="H57" s="1">
-        <v>339550</v>
+      <c r="O57" s="1">
+        <v>2.2370204</v>
+      </c>
+      <c r="P57" s="1">
+        <v>3.8546705</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>5.70917623</v>
+      </c>
+      <c r="S57" s="9">
+        <v>3.46075053</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8">
         <v>43525</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="1">
+        <v>1564664</v>
+      </c>
+      <c r="C58" s="10">
+        <v>-3.89733103</v>
+      </c>
+      <c r="D58" s="1">
+        <v>6600.12739729</v>
+      </c>
+      <c r="E58" s="1">
+        <v>300209</v>
+      </c>
+      <c r="F58" s="9">
         <v>3.13840803</v>
       </c>
-      <c r="C58" s="1">
+      <c r="H58" s="1">
+        <v>106200</v>
+      </c>
+      <c r="I58" s="1">
+        <v>106506</v>
+      </c>
+      <c r="J58" s="1">
         <v>84.31584076999999</v>
       </c>
-      <c r="G58" s="1">
-        <v>1564664</v>
-      </c>
-      <c r="H58" s="1">
-        <v>300209</v>
+      <c r="O58" s="1">
+        <v>2.16845431</v>
+      </c>
+      <c r="P58" s="1">
+        <v>2.5226588</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>5.83333157</v>
+      </c>
+      <c r="R58" s="1">
+        <v>60553.33333333</v>
+      </c>
+      <c r="S58" s="9">
+        <v>3.13840803</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8">
         <v>43556</v>
       </c>
-      <c r="B59" s="9">
+      <c r="B59" s="1">
+        <v>1596724</v>
+      </c>
+      <c r="E59" s="1">
+        <v>302098</v>
+      </c>
+      <c r="F59" s="9">
         <v>3.22580519</v>
       </c>
-      <c r="C59" s="1">
+      <c r="H59" s="1">
+        <v>95076</v>
+      </c>
+      <c r="I59" s="1">
+        <v>120225</v>
+      </c>
+      <c r="J59" s="1">
         <v>85.42491032</v>
       </c>
-      <c r="G59" s="1">
-        <v>1596724</v>
-      </c>
-      <c r="H59" s="1">
-        <v>302098</v>
+      <c r="O59" s="1">
+        <v>2.25034157</v>
+      </c>
+      <c r="P59" s="1">
+        <v>2.40081907</v>
+      </c>
+      <c r="Q59" s="1">
+        <v>5.88762498</v>
+      </c>
+      <c r="S59" s="9">
+        <v>3.22580519</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8">
         <v>43586</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60" s="1">
+        <v>1487791</v>
+      </c>
+      <c r="E60" s="1">
+        <v>283445</v>
+      </c>
+      <c r="F60" s="9">
         <v>3.53097759</v>
       </c>
-      <c r="C60" s="1">
+      <c r="H60" s="1">
+        <v>106518</v>
+      </c>
+      <c r="I60" s="1">
+        <v>182727</v>
+      </c>
+      <c r="J60" s="1">
         <v>81.99167469</v>
       </c>
-      <c r="G60" s="1">
-        <v>1487791</v>
-      </c>
-      <c r="H60" s="1">
-        <v>283445</v>
+      <c r="O60" s="1">
+        <v>2.27294425</v>
+      </c>
+      <c r="P60" s="1">
+        <v>2.74509917</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>5.77301386</v>
+      </c>
+      <c r="S60" s="9">
+        <v>3.53097759</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8">
         <v>43617</v>
       </c>
-      <c r="B61" s="9">
+      <c r="B61" s="1">
+        <v>1551847</v>
+      </c>
+      <c r="C61" s="10">
+        <v>-2.19831064</v>
+      </c>
+      <c r="D61" s="1">
+        <v>13165.79436414</v>
+      </c>
+      <c r="E61" s="1">
+        <v>266107</v>
+      </c>
+      <c r="F61" s="9">
         <v>3.62905843</v>
       </c>
-      <c r="C61" s="1">
+      <c r="H61" s="1">
+        <v>102074</v>
+      </c>
+      <c r="I61" s="1">
+        <v>144118</v>
+      </c>
+      <c r="J61" s="1">
         <v>86.14354211</v>
       </c>
-      <c r="G61" s="1">
-        <v>1551847</v>
-      </c>
-      <c r="H61" s="1">
-        <v>266107</v>
+      <c r="O61" s="1">
+        <v>2.47559626</v>
+      </c>
+      <c r="P61" s="1">
+        <v>2.82186071</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>6.80452525</v>
+      </c>
+      <c r="R61" s="1">
+        <v>60427.33333333</v>
+      </c>
+      <c r="S61" s="9">
+        <v>3.62905843</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8">
         <v>43647</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62" s="1">
+        <v>1802593</v>
+      </c>
+      <c r="E62" s="1">
+        <v>389503</v>
+      </c>
+      <c r="F62" s="9">
         <v>3.43946386</v>
       </c>
-      <c r="C62" s="1">
+      <c r="H62" s="1">
+        <v>93071</v>
+      </c>
+      <c r="I62" s="1">
+        <v>112026</v>
+      </c>
+      <c r="J62" s="1">
         <v>93.90137844</v>
       </c>
-      <c r="G62" s="1">
-        <v>1802593</v>
-      </c>
-      <c r="H62" s="1">
-        <v>389503</v>
+      <c r="O62" s="1">
+        <v>2.461632</v>
+      </c>
+      <c r="P62" s="1">
+        <v>3.32254543</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>5.90833563</v>
+      </c>
+      <c r="S62" s="9">
+        <v>3.43946386</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8">
         <v>43678</v>
       </c>
-      <c r="B63" s="9">
+      <c r="B63" s="1">
+        <v>1736102</v>
+      </c>
+      <c r="E63" s="1">
+        <v>397070</v>
+      </c>
+      <c r="F63" s="9">
         <v>3.56279607</v>
       </c>
-      <c r="C63" s="1">
+      <c r="H63" s="1">
+        <v>100225</v>
+      </c>
+      <c r="I63" s="1">
+        <v>108736</v>
+      </c>
+      <c r="J63" s="1">
         <v>92.44163528</v>
       </c>
-      <c r="G63" s="1">
-        <v>1736102</v>
-      </c>
-      <c r="H63" s="1">
-        <v>397070</v>
+      <c r="O63" s="1">
+        <v>2.34149569</v>
+      </c>
+      <c r="P63" s="1">
+        <v>3.75589246</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>5.89608868</v>
+      </c>
+      <c r="S63" s="9">
+        <v>3.56279607</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8">
         <v>43709</v>
       </c>
-      <c r="B64" s="9">
+      <c r="B64" s="1">
+        <v>1463543</v>
+      </c>
+      <c r="C64" s="10">
+        <v>-0.29928553</v>
+      </c>
+      <c r="D64" s="1">
+        <v>20548.88298768</v>
+      </c>
+      <c r="E64" s="1">
+        <v>248568</v>
+      </c>
+      <c r="F64" s="9">
         <v>3.29870521</v>
       </c>
-      <c r="C64" s="1">
+      <c r="H64" s="1">
+        <v>98438</v>
+      </c>
+      <c r="I64" s="1">
+        <v>105075</v>
+      </c>
+      <c r="J64" s="1">
         <v>87.13118264000001</v>
       </c>
-      <c r="G64" s="1">
-        <v>1463543</v>
-      </c>
-      <c r="H64" s="1">
-        <v>248568</v>
+      <c r="O64" s="1">
+        <v>2.28718749</v>
+      </c>
+      <c r="P64" s="1">
+        <v>2.94587295</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>5.83518802</v>
+      </c>
+      <c r="R64" s="1">
+        <v>61159.33333333</v>
+      </c>
+      <c r="S64" s="9">
+        <v>3.29870521</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8">
         <v>43739</v>
       </c>
-      <c r="B65" s="9">
+      <c r="B65" s="1">
+        <v>1530479</v>
+      </c>
+      <c r="E65" s="1">
+        <v>258611</v>
+      </c>
+      <c r="F65" s="9">
         <v>3.26773754</v>
       </c>
-      <c r="C65" s="1">
+      <c r="H65" s="1">
+        <v>97378</v>
+      </c>
+      <c r="I65" s="1">
+        <v>116182</v>
+      </c>
+      <c r="J65" s="1">
         <v>86.92346615</v>
       </c>
-      <c r="G65" s="1">
-        <v>1530479</v>
-      </c>
-      <c r="H65" s="1">
-        <v>258611</v>
+      <c r="O65" s="1">
+        <v>2.23429448</v>
+      </c>
+      <c r="P65" s="1">
+        <v>2.84514289</v>
+      </c>
+      <c r="Q65" s="1">
+        <v>5.5834928</v>
+      </c>
+      <c r="S65" s="9">
+        <v>3.26773754</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8">
         <v>43770</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="1">
+        <v>1533668</v>
+      </c>
+      <c r="E66" s="1">
+        <v>248636</v>
+      </c>
+      <c r="F66" s="9">
         <v>3.12624712</v>
       </c>
-      <c r="C66" s="1">
+      <c r="H66" s="1">
+        <v>111473</v>
+      </c>
+      <c r="I66" s="1">
+        <v>113717</v>
+      </c>
+      <c r="J66" s="1">
         <v>88.82490473</v>
       </c>
-      <c r="G66" s="1">
-        <v>1533668</v>
-      </c>
-      <c r="H66" s="1">
-        <v>248636</v>
+      <c r="O66" s="1">
+        <v>2.20129599</v>
+      </c>
+      <c r="P66" s="1">
+        <v>2.51085652</v>
+      </c>
+      <c r="Q66" s="1">
+        <v>5.37549551</v>
+      </c>
+      <c r="S66" s="9">
+        <v>3.12624712</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8">
         <v>43800</v>
       </c>
-      <c r="B67" s="9">
+      <c r="B67" s="1">
+        <v>1724961</v>
+      </c>
+      <c r="C67" s="1">
+        <v>2.77176985</v>
+      </c>
+      <c r="D67" s="1">
+        <v>27688.50119434</v>
+      </c>
+      <c r="E67" s="1">
+        <v>272742</v>
+      </c>
+      <c r="F67" s="9">
         <v>3.12875261</v>
       </c>
-      <c r="C67" s="1">
+      <c r="G67" s="1">
+        <v>1448.79934364</v>
+      </c>
+      <c r="H67" s="1">
+        <v>133278</v>
+      </c>
+      <c r="I67" s="1">
+        <v>115193</v>
+      </c>
+      <c r="J67" s="1">
         <v>82.98612626000001</v>
       </c>
-      <c r="D67" s="1">
-        <v>1448.79934364</v>
-      </c>
-      <c r="E67" s="1">
-        <v>27688.50119434</v>
-      </c>
-      <c r="F67" s="1">
+      <c r="K67" s="1">
         <v>3.35528749</v>
       </c>
-      <c r="G67" s="1">
-        <v>1724961</v>
-      </c>
-      <c r="H67" s="1">
-        <v>272742</v>
+      <c r="L67" s="1">
+        <v>1137.10496244</v>
+      </c>
+      <c r="M67" s="1">
+        <v>1145.19467003</v>
+      </c>
+      <c r="N67" s="1">
+        <v>600.78175724</v>
+      </c>
+      <c r="O67" s="1">
+        <v>2.53379217</v>
+      </c>
+      <c r="P67" s="1">
+        <v>2.58765324</v>
+      </c>
+      <c r="Q67" s="1">
+        <v>5.68740972</v>
+      </c>
+      <c r="R67" s="1">
+        <v>63166.33333333</v>
+      </c>
+      <c r="S67" s="9">
+        <v>3.12875261</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8">
         <v>43831</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68" s="1">
+        <v>1688102</v>
+      </c>
+      <c r="E68" s="1">
+        <v>329047</v>
+      </c>
+      <c r="F68" s="9">
         <v>3.49179666</v>
       </c>
-      <c r="C68" s="1">
+      <c r="H68" s="1">
+        <v>90720</v>
+      </c>
+      <c r="I68" s="1">
+        <v>99643</v>
+      </c>
+      <c r="J68" s="1">
         <v>82.95028855</v>
       </c>
-      <c r="G68" s="1">
-        <v>1688102</v>
-      </c>
-      <c r="H68" s="1">
-        <v>329047</v>
+      <c r="O68" s="1">
+        <v>2.38235867</v>
+      </c>
+      <c r="P68" s="1">
+        <v>3.34768303</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>6.08770662</v>
+      </c>
+      <c r="S68" s="9">
+        <v>3.49179666</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8">
         <v>43862</v>
       </c>
-      <c r="B69" s="9">
+      <c r="B69" s="1">
+        <v>732966</v>
+      </c>
+      <c r="E69" s="1">
+        <v>6222</v>
+      </c>
+      <c r="F69" s="9">
         <v>4.04788206</v>
       </c>
-      <c r="C69" s="1">
+      <c r="H69" s="1">
+        <v>40829</v>
+      </c>
+      <c r="I69" s="1">
+        <v>52946</v>
+      </c>
+      <c r="J69" s="1">
         <v>49.05792106</v>
       </c>
-      <c r="G69" s="1">
-        <v>732966</v>
-      </c>
-      <c r="H69" s="1">
-        <v>6222</v>
+      <c r="O69" s="1">
+        <v>2.68083475</v>
+      </c>
+      <c r="P69" s="1">
+        <v>13.55402163</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>7.62022015</v>
+      </c>
+      <c r="S69" s="9">
+        <v>4.04788206</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8">
         <v>43891</v>
       </c>
-      <c r="B70" s="9">
+      <c r="B70" s="1">
+        <v>240001</v>
+      </c>
+      <c r="C70" s="10">
+        <v>-38.95046046</v>
+      </c>
+      <c r="D70" s="1">
+        <v>4029.34738486</v>
+      </c>
+      <c r="E70" s="1">
+        <v>1488</v>
+      </c>
+      <c r="F70" s="9">
         <v>5.82018094</v>
       </c>
-      <c r="C70" s="1">
+      <c r="H70" s="1">
+        <v>14887</v>
+      </c>
+      <c r="I70" s="1">
+        <v>17848</v>
+      </c>
+      <c r="J70" s="1">
         <v>40.16224463</v>
       </c>
-      <c r="G70" s="1">
-        <v>240001</v>
-      </c>
-      <c r="H70" s="1">
-        <v>1488</v>
+      <c r="O70" s="1">
+        <v>3.31443001</v>
+      </c>
+      <c r="P70" s="1">
+        <v>45.13041395</v>
+      </c>
+      <c r="Q70" s="1">
+        <v>13.67747481</v>
+      </c>
+      <c r="R70" s="1">
+        <v>63246</v>
+      </c>
+      <c r="S70" s="9">
+        <v>5.82018094</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8">
         <v>43922</v>
       </c>
-      <c r="B71" s="9">
+      <c r="B71" s="1">
+        <v>750</v>
+      </c>
+      <c r="E71" s="1">
+        <v>18</v>
+      </c>
+      <c r="F71" s="9">
         <v>39.1238523</v>
       </c>
-      <c r="C71" s="1">
+      <c r="H71" s="1">
+        <v>96</v>
+      </c>
+      <c r="I71" s="1">
+        <v>87</v>
+      </c>
+      <c r="J71" s="1">
         <v>40.43375004</v>
       </c>
-      <c r="G71" s="1">
-        <v>750</v>
-      </c>
-      <c r="H71" s="1">
-        <v>18</v>
+      <c r="O71" s="1">
+        <v>24.56088561</v>
+      </c>
+      <c r="P71" s="1">
+        <v>58.89917355</v>
+      </c>
+      <c r="Q71" s="1">
+        <v>40.8125</v>
+      </c>
+      <c r="S71" s="9">
+        <v>39.1238523</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8">
         <v>43952</v>
       </c>
-      <c r="B72" s="9">
+      <c r="B72" s="1">
+        <v>880</v>
+      </c>
+      <c r="E72" s="1">
+        <v>23</v>
+      </c>
+      <c r="F72" s="9">
         <v>51.88531995</v>
       </c>
-      <c r="C72" s="1">
+      <c r="H72" s="1">
+        <v>157</v>
+      </c>
+      <c r="I72" s="1">
+        <v>79</v>
+      </c>
+      <c r="J72" s="1">
         <v>59.25552389</v>
       </c>
-      <c r="G72" s="1">
-        <v>880</v>
-      </c>
-      <c r="H72" s="1">
-        <v>23</v>
+      <c r="O72" s="1">
+        <v>35.87152778</v>
+      </c>
+      <c r="P72" s="1">
+        <v>59.58695652</v>
+      </c>
+      <c r="Q72" s="1">
+        <v>56.23364486</v>
+      </c>
+      <c r="S72" s="9">
+        <v>51.88531995</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8">
         <v>43983</v>
       </c>
-      <c r="B73" s="9">
+      <c r="B73" s="1">
+        <v>2171</v>
+      </c>
+      <c r="C73" s="10">
+        <v>-68.2012548</v>
+      </c>
+      <c r="D73" s="1">
+        <v>4186.55740391</v>
+      </c>
+      <c r="E73" s="1">
+        <v>118</v>
+      </c>
+      <c r="F73" s="9">
         <v>55.33914769</v>
       </c>
-      <c r="C73" s="1">
+      <c r="H73" s="1">
+        <v>464</v>
+      </c>
+      <c r="I73" s="1">
+        <v>130</v>
+      </c>
+      <c r="J73" s="1">
         <v>57.04914877</v>
       </c>
-      <c r="G73" s="1">
-        <v>2171</v>
-      </c>
-      <c r="H73" s="1">
-        <v>118</v>
+      <c r="O73" s="1">
+        <v>24.69172932</v>
+      </c>
+      <c r="P73" s="1">
+        <v>59.77891654</v>
+      </c>
+      <c r="Q73" s="1">
+        <v>59.94892704</v>
+      </c>
+      <c r="R73" s="1">
+        <v>62319</v>
+      </c>
+      <c r="S73" s="9">
+        <v>55.33914769</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8">
         <v>44013</v>
       </c>
-      <c r="B74" s="9">
+      <c r="B74" s="1">
+        <v>6843</v>
+      </c>
+      <c r="E74" s="1">
+        <v>958</v>
+      </c>
+      <c r="F74" s="9">
         <v>52.7038721</v>
       </c>
-      <c r="C74" s="1">
+      <c r="H74" s="1">
+        <v>626</v>
+      </c>
+      <c r="I74" s="1">
+        <v>634</v>
+      </c>
+      <c r="J74" s="1">
         <v>66.39148729999999</v>
       </c>
-      <c r="G74" s="1">
-        <v>6843</v>
-      </c>
-      <c r="H74" s="1">
-        <v>958</v>
+      <c r="O74" s="1">
+        <v>21.613879</v>
+      </c>
+      <c r="P74" s="1">
+        <v>59.28813559</v>
+      </c>
+      <c r="Q74" s="1">
+        <v>59.87656904</v>
+      </c>
+      <c r="S74" s="9">
+        <v>52.7038721</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8">
         <v>44044</v>
       </c>
-      <c r="B75" s="9">
+      <c r="B75" s="1">
+        <v>8912</v>
+      </c>
+      <c r="E75" s="1">
+        <v>2163</v>
+      </c>
+      <c r="F75" s="9">
         <v>47.51534443</v>
       </c>
-      <c r="C75" s="1">
+      <c r="H75" s="1">
+        <v>718</v>
+      </c>
+      <c r="I75" s="1">
+        <v>581</v>
+      </c>
+      <c r="J75" s="1">
         <v>64.75495642</v>
       </c>
-      <c r="G75" s="1">
-        <v>8912</v>
-      </c>
-      <c r="H75" s="1">
-        <v>2163</v>
+      <c r="O75" s="1">
+        <v>6.72691293</v>
+      </c>
+      <c r="P75" s="1">
+        <v>56.45116279</v>
+      </c>
+      <c r="Q75" s="1">
+        <v>59.17693837</v>
+      </c>
+      <c r="S75" s="9">
+        <v>47.51534443</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8">
         <v>44075</v>
       </c>
-      <c r="B76" s="9">
+      <c r="B76" s="1">
+        <v>9500</v>
+      </c>
+      <c r="C76" s="10">
+        <v>-78.41413439999999</v>
+      </c>
+      <c r="D76" s="1">
+        <v>4435.65426399</v>
+      </c>
+      <c r="E76" s="1">
+        <v>2422</v>
+      </c>
+      <c r="F76" s="9">
         <v>33.89752066</v>
       </c>
-      <c r="C76" s="1">
+      <c r="H76" s="1">
+        <v>1063</v>
+      </c>
+      <c r="I76" s="1">
+        <v>394</v>
+      </c>
+      <c r="J76" s="1">
         <v>63.12299737</v>
       </c>
-      <c r="G76" s="1">
-        <v>9500</v>
-      </c>
-      <c r="H76" s="1">
-        <v>2422</v>
+      <c r="O76" s="1">
+        <v>5.33692308</v>
+      </c>
+      <c r="P76" s="1">
+        <v>51.6957672</v>
+      </c>
+      <c r="Q76" s="1">
+        <v>58.79473684</v>
+      </c>
+      <c r="R76" s="1">
+        <v>62282.66666667</v>
+      </c>
+      <c r="S76" s="9">
+        <v>33.89752066</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8">
         <v>44105</v>
       </c>
-      <c r="B77" s="9">
+      <c r="B77" s="1">
+        <v>13399</v>
+      </c>
+      <c r="E77" s="1">
+        <v>3169</v>
+      </c>
+      <c r="F77" s="9">
         <v>27.46355685</v>
       </c>
-      <c r="C77" s="1">
+      <c r="H77" s="1">
+        <v>1415</v>
+      </c>
+      <c r="I77" s="1">
+        <v>428</v>
+      </c>
+      <c r="J77" s="1">
         <v>57.59082346</v>
       </c>
-      <c r="G77" s="1">
-        <v>13399</v>
-      </c>
-      <c r="H77" s="1">
-        <v>3169</v>
+      <c r="O77" s="1">
+        <v>3.52638889</v>
+      </c>
+      <c r="P77" s="1">
+        <v>50.58052885</v>
+      </c>
+      <c r="Q77" s="1">
+        <v>57.26190476</v>
+      </c>
+      <c r="S77" s="9">
+        <v>27.46355685</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8">
         <v>44136</v>
       </c>
-      <c r="B78" s="9">
+      <c r="B78" s="1">
+        <v>14749</v>
+      </c>
+      <c r="E78" s="1">
+        <v>4007</v>
+      </c>
+      <c r="F78" s="9">
         <v>23.07268519</v>
       </c>
-      <c r="C78" s="1">
+      <c r="H78" s="1">
+        <v>1270</v>
+      </c>
+      <c r="I78" s="1">
+        <v>500</v>
+      </c>
+      <c r="J78" s="1">
         <v>54.16829902</v>
       </c>
-      <c r="G78" s="1">
-        <v>14749</v>
-      </c>
-      <c r="H78" s="1">
-        <v>4007</v>
+      <c r="O78" s="1">
+        <v>3.69428969</v>
+      </c>
+      <c r="P78" s="1">
+        <v>32.02759382</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>55.890625</v>
+      </c>
+      <c r="S78" s="9">
+        <v>23.07268519</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8">
         <v>44166</v>
       </c>
-      <c r="B79" s="9">
+      <c r="B79" s="1">
+        <v>24170</v>
+      </c>
+      <c r="C79" s="10">
+        <v>-82.55588213999999</v>
+      </c>
+      <c r="D79" s="1">
+        <v>4830.01478136</v>
+      </c>
+      <c r="E79" s="1">
+        <v>7657</v>
+      </c>
+      <c r="F79" s="9">
         <v>20.43128984</v>
       </c>
-      <c r="C79" s="1">
+      <c r="G79" s="1">
+        <v>1761.7722066</v>
+      </c>
+      <c r="H79" s="1">
+        <v>1405</v>
+      </c>
+      <c r="I79" s="1">
+        <v>2252</v>
+      </c>
+      <c r="J79" s="1">
         <v>62.04792085</v>
       </c>
-      <c r="D79" s="1">
-        <v>1761.7722066</v>
-      </c>
-      <c r="E79" s="1">
-        <v>4830.01478136</v>
-      </c>
-      <c r="F79" s="1">
+      <c r="K79" s="1">
         <v>4.2866862</v>
       </c>
-      <c r="G79" s="1">
-        <v>24170</v>
-      </c>
-      <c r="H79" s="1">
-        <v>7657</v>
+      <c r="L79" s="1">
+        <v>1746.5691043</v>
+      </c>
+      <c r="M79" s="1">
+        <v>1656.51113724</v>
+      </c>
+      <c r="N79" s="1">
+        <v>875.71578834</v>
+      </c>
+      <c r="O79" s="1">
+        <v>7.37695313</v>
+      </c>
+      <c r="P79" s="1">
+        <v>19.99013367</v>
+      </c>
+      <c r="Q79" s="1">
+        <v>52.32394366</v>
+      </c>
+      <c r="R79" s="1">
+        <v>62685.66666667</v>
+      </c>
+      <c r="S79" s="9">
+        <v>20.43128984</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8">
         <v>44197</v>
       </c>
-      <c r="B80" s="9">
+      <c r="B80" s="1">
+        <v>23366</v>
+      </c>
+      <c r="E80" s="1">
+        <v>6599</v>
+      </c>
+      <c r="F80" s="9">
         <v>23.05956404</v>
       </c>
-      <c r="C80" s="1">
+      <c r="H80" s="1">
+        <v>1255</v>
+      </c>
+      <c r="I80" s="1">
+        <v>3946</v>
+      </c>
+      <c r="J80" s="1">
         <v>44.31327241</v>
       </c>
-      <c r="G80" s="1">
-        <v>23366</v>
-      </c>
-      <c r="H80" s="1">
-        <v>6599</v>
+      <c r="O80" s="1">
+        <v>8.978666670000001</v>
+      </c>
+      <c r="P80" s="1">
+        <v>22.32843137</v>
+      </c>
+      <c r="Q80" s="1">
+        <v>45.28142077</v>
+      </c>
+      <c r="S80" s="9">
+        <v>23.05956404</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8">
         <v>44228</v>
       </c>
-      <c r="B81" s="9">
+      <c r="B81" s="1">
+        <v>18141</v>
+      </c>
+      <c r="E81" s="1">
+        <v>4498</v>
+      </c>
+      <c r="F81" s="9">
         <v>26.21096654</v>
       </c>
-      <c r="C81" s="1">
+      <c r="H81" s="1">
+        <v>1130</v>
+      </c>
+      <c r="I81" s="1">
+        <v>3215</v>
+      </c>
+      <c r="J81" s="1">
         <v>44.1696703</v>
       </c>
-      <c r="G81" s="1">
-        <v>18141</v>
-      </c>
-      <c r="H81" s="1">
-        <v>4498</v>
+      <c r="O81" s="1">
+        <v>6.35108025</v>
+      </c>
+      <c r="P81" s="1">
+        <v>27.01617076</v>
+      </c>
+      <c r="Q81" s="1">
+        <v>48.61437908</v>
+      </c>
+      <c r="S81" s="9">
+        <v>26.21096654</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8">
         <v>44256</v>
       </c>
-      <c r="B82" s="9">
+      <c r="B82" s="1">
+        <v>27202</v>
+      </c>
+      <c r="C82" s="10">
+        <v>-89.46434057</v>
+      </c>
+      <c r="D82" s="1">
+        <v>424.51831782</v>
+      </c>
+      <c r="E82" s="1">
+        <v>8892</v>
+      </c>
+      <c r="F82" s="9">
         <v>27.45040486</v>
       </c>
-      <c r="C82" s="1">
+      <c r="H82" s="1">
+        <v>1530</v>
+      </c>
+      <c r="I82" s="1">
+        <v>4193</v>
+      </c>
+      <c r="J82" s="1">
         <v>51.42837194</v>
       </c>
-      <c r="G82" s="1">
-        <v>27202</v>
-      </c>
-      <c r="H82" s="1">
-        <v>8892</v>
+      <c r="O82" s="1">
+        <v>5.50432099</v>
+      </c>
+      <c r="P82" s="1">
+        <v>25.46971473</v>
+      </c>
+      <c r="Q82" s="1">
+        <v>47.92355372</v>
+      </c>
+      <c r="R82" s="1">
+        <v>61884.33333333</v>
+      </c>
+      <c r="S82" s="9">
+        <v>27.45040486</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8">
         <v>44287</v>
       </c>
-      <c r="B83" s="9">
+      <c r="B83" s="1">
+        <v>25737</v>
+      </c>
+      <c r="E83" s="1">
+        <v>9056</v>
+      </c>
+      <c r="F83" s="9">
         <v>28.88426966</v>
       </c>
-      <c r="C83" s="1">
+      <c r="H83" s="1">
+        <v>1442</v>
+      </c>
+      <c r="I83" s="1">
+        <v>3729</v>
+      </c>
+      <c r="J83" s="1">
         <v>52.70180653</v>
       </c>
-      <c r="G83" s="1">
-        <v>25737</v>
-      </c>
-      <c r="H83" s="1">
-        <v>9056</v>
+      <c r="O83" s="1">
+        <v>9.788275860000001</v>
+      </c>
+      <c r="P83" s="1">
+        <v>28.5663282</v>
+      </c>
+      <c r="Q83" s="1">
+        <v>50.703125</v>
+      </c>
+      <c r="S83" s="9">
+        <v>28.88426966</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8">
         <v>44317</v>
       </c>
-      <c r="B84" s="9">
+      <c r="B84" s="1">
+        <v>14190</v>
+      </c>
+      <c r="E84" s="1">
+        <v>7388</v>
+      </c>
+      <c r="F84" s="9">
         <v>28.22909473</v>
       </c>
-      <c r="C84" s="1">
+      <c r="H84" s="1">
+        <v>844</v>
+      </c>
+      <c r="I84" s="1">
+        <v>84</v>
+      </c>
+      <c r="J84" s="1">
         <v>52.93948793</v>
       </c>
-      <c r="G84" s="1">
-        <v>14190</v>
-      </c>
-      <c r="H84" s="1">
-        <v>7388</v>
+      <c r="O84" s="1">
+        <v>8.626937979999999</v>
+      </c>
+      <c r="P84" s="1">
+        <v>27.40350659</v>
+      </c>
+      <c r="Q84" s="1">
+        <v>52.19354839</v>
+      </c>
+      <c r="S84" s="9">
+        <v>28.22909473</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="8">
         <v>44348</v>
       </c>
-      <c r="B85" s="9">
+      <c r="B85" s="1">
+        <v>10029</v>
+      </c>
+      <c r="C85" s="10">
+        <v>-80.23094848</v>
+      </c>
+      <c r="D85" s="1">
+        <v>827.64269004</v>
+      </c>
+      <c r="E85" s="1">
+        <v>6983</v>
+      </c>
+      <c r="F85" s="9">
         <v>33.75115951</v>
       </c>
-      <c r="C85" s="1">
+      <c r="H85" s="1">
+        <v>402</v>
+      </c>
+      <c r="I85" s="1">
+        <v>12</v>
+      </c>
+      <c r="J85" s="1">
         <v>54.64458579</v>
       </c>
-      <c r="G85" s="1">
-        <v>10029</v>
-      </c>
-      <c r="H85" s="1">
-        <v>6983</v>
+      <c r="O85" s="1">
+        <v>11.30204778</v>
+      </c>
+      <c r="P85" s="1">
+        <v>29.82980483</v>
+      </c>
+      <c r="Q85" s="1">
+        <v>58</v>
+      </c>
+      <c r="R85" s="1">
+        <v>61030</v>
+      </c>
+      <c r="S85" s="9">
+        <v>33.75115951</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8">
         <v>44378</v>
       </c>
-      <c r="B86" s="9">
+      <c r="B86" s="1">
+        <v>18517</v>
+      </c>
+      <c r="E86" s="1">
+        <v>12669</v>
+      </c>
+      <c r="F86" s="9">
         <v>29.33472068</v>
       </c>
-      <c r="C86" s="1">
+      <c r="H86" s="1">
+        <v>554</v>
+      </c>
+      <c r="I86" s="1">
+        <v>332</v>
+      </c>
+      <c r="J86" s="1">
         <v>56.08845627</v>
       </c>
-      <c r="G86" s="1">
-        <v>18517</v>
-      </c>
-      <c r="H86" s="1">
-        <v>12669</v>
+      <c r="O86" s="1">
+        <v>12.64380531</v>
+      </c>
+      <c r="P86" s="1">
+        <v>26.87197786</v>
+      </c>
+      <c r="Q86" s="1">
+        <v>60</v>
+      </c>
+      <c r="S86" s="9">
+        <v>29.33472068</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="8">
         <v>44409</v>
       </c>
-      <c r="B87" s="9">
+      <c r="B87" s="1">
+        <v>15887</v>
+      </c>
+      <c r="E87" s="1">
+        <v>8907</v>
+      </c>
+      <c r="F87" s="9">
         <v>26.57441124</v>
       </c>
-      <c r="C87" s="1">
+      <c r="H87" s="1">
+        <v>683</v>
+      </c>
+      <c r="I87" s="1">
+        <v>95</v>
+      </c>
+      <c r="J87" s="1">
         <v>56.07651831</v>
       </c>
-      <c r="G87" s="1">
-        <v>15887</v>
-      </c>
-      <c r="H87" s="1">
-        <v>8907</v>
+      <c r="O87" s="1">
+        <v>12.12820513</v>
+      </c>
+      <c r="P87" s="1">
+        <v>24.12330129</v>
+      </c>
+      <c r="Q87" s="1">
+        <v>56.95731707</v>
+      </c>
+      <c r="S87" s="9">
+        <v>26.57441124</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="8">
         <v>44440</v>
       </c>
-      <c r="B88" s="9">
+      <c r="B88" s="1">
+        <v>19009</v>
+      </c>
+      <c r="C88" s="10">
+        <v>-73.17857092</v>
+      </c>
+      <c r="D88" s="1">
+        <v>1189.70586264</v>
+      </c>
+      <c r="E88" s="1">
+        <v>8952</v>
+      </c>
+      <c r="F88" s="9">
         <v>24.58633022</v>
       </c>
-      <c r="C88" s="1">
+      <c r="H88" s="1">
+        <v>797</v>
+      </c>
+      <c r="I88" s="1">
+        <v>678</v>
+      </c>
+      <c r="J88" s="1">
         <v>65.10329204999999</v>
       </c>
-      <c r="G88" s="1">
-        <v>19009</v>
-      </c>
-      <c r="H88" s="1">
-        <v>8952</v>
+      <c r="O88" s="1">
+        <v>8.954166669999999</v>
+      </c>
+      <c r="P88" s="1">
+        <v>23.70268817</v>
+      </c>
+      <c r="Q88" s="1">
+        <v>58.84177215</v>
+      </c>
+      <c r="R88" s="1">
+        <v>59714.33333333</v>
+      </c>
+      <c r="S88" s="9">
+        <v>24.58633022</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="8">
         <v>44470</v>
       </c>
-      <c r="B89" s="9">
+      <c r="B89" s="1">
+        <v>24006</v>
+      </c>
+      <c r="E89" s="1">
+        <v>6065</v>
+      </c>
+      <c r="F89" s="9">
         <v>25.03605994</v>
       </c>
-      <c r="C89" s="1">
+      <c r="H89" s="1">
+        <v>2104</v>
+      </c>
+      <c r="I89" s="1">
+        <v>2936</v>
+      </c>
+      <c r="J89" s="1">
         <v>64.36182587</v>
       </c>
-      <c r="G89" s="1">
-        <v>24006</v>
-      </c>
-      <c r="H89" s="1">
-        <v>6065</v>
+      <c r="O89" s="1">
+        <v>9.51829268</v>
+      </c>
+      <c r="P89" s="1">
+        <v>24.83218884</v>
+      </c>
+      <c r="Q89" s="1">
+        <v>53.305</v>
+      </c>
+      <c r="S89" s="9">
+        <v>25.03605994</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8">
         <v>44501</v>
       </c>
-      <c r="B90" s="9">
+      <c r="B90" s="1">
+        <v>41179</v>
+      </c>
+      <c r="E90" s="1">
+        <v>3479</v>
+      </c>
+      <c r="F90" s="9">
         <v>16.08366534</v>
       </c>
-      <c r="C90" s="1">
+      <c r="H90" s="1">
+        <v>2537</v>
+      </c>
+      <c r="I90" s="1">
+        <v>7488</v>
+      </c>
+      <c r="J90" s="1">
         <v>78.01185369</v>
       </c>
-      <c r="G90" s="1">
-        <v>41179</v>
-      </c>
-      <c r="H90" s="1">
-        <v>3479</v>
+      <c r="O90" s="1">
+        <v>11.25725594</v>
+      </c>
+      <c r="P90" s="1">
+        <v>31.32855626</v>
+      </c>
+      <c r="Q90" s="1">
+        <v>36.70714286</v>
+      </c>
+      <c r="S90" s="9">
+        <v>16.08366534</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="8">
         <v>44531</v>
       </c>
-      <c r="B91" s="9">
+      <c r="B91" s="1">
+        <v>92796</v>
+      </c>
+      <c r="C91" s="10">
+        <v>-60.79450798</v>
+      </c>
+      <c r="D91" s="1">
+        <v>1893.63105965</v>
+      </c>
+      <c r="E91" s="1">
+        <v>4764</v>
+      </c>
+      <c r="F91" s="9">
         <v>13.19731529</v>
       </c>
-      <c r="C91" s="1">
+      <c r="G91" s="1">
+        <v>5737.25018756</v>
+      </c>
+      <c r="H91" s="1">
+        <v>10939</v>
+      </c>
+      <c r="I91" s="1">
+        <v>27672</v>
+      </c>
+      <c r="J91" s="1">
         <v>74.31743125</v>
       </c>
-      <c r="D91" s="1">
-        <v>5737.25018756</v>
-      </c>
-      <c r="E91" s="1">
-        <v>1893.63105965</v>
-      </c>
-      <c r="F91" s="1">
+      <c r="K91" s="1">
         <v>22.41620607</v>
       </c>
-      <c r="G91" s="1">
-        <v>92796</v>
-      </c>
-      <c r="H91" s="1">
-        <v>4764</v>
+      <c r="L91" s="1">
+        <v>6083.23257082</v>
+      </c>
+      <c r="M91" s="1">
+        <v>1742.17316816</v>
+      </c>
+      <c r="N91" s="1">
+        <v>2827.48085763</v>
+      </c>
+      <c r="O91" s="1">
+        <v>9.15538063</v>
+      </c>
+      <c r="P91" s="1">
+        <v>27.65915119</v>
+      </c>
+      <c r="Q91" s="1">
+        <v>14.03726083</v>
+      </c>
+      <c r="R91" s="1">
+        <v>59831.33333333</v>
+      </c>
+      <c r="S91" s="9">
+        <v>13.19731529</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8">
         <v>44562</v>
       </c>
-      <c r="B92" s="9">
+      <c r="B92" s="1">
+        <v>57174</v>
+      </c>
+      <c r="E92" s="1">
+        <v>4361</v>
+      </c>
+      <c r="F92" s="9">
         <v>18.81575577</v>
       </c>
-      <c r="C92" s="1">
+      <c r="H92" s="1">
+        <v>5203</v>
+      </c>
+      <c r="I92" s="1">
+        <v>11428</v>
+      </c>
+      <c r="J92" s="1">
         <v>57.53170374</v>
       </c>
-      <c r="G92" s="1">
-        <v>57174</v>
-      </c>
-      <c r="H92" s="1">
-        <v>4361</v>
+      <c r="O92" s="1">
+        <v>15.69590164</v>
+      </c>
+      <c r="P92" s="1">
+        <v>29.72991071</v>
+      </c>
+      <c r="Q92" s="1">
+        <v>23.71711754</v>
+      </c>
+      <c r="S92" s="9">
+        <v>18.81575577</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="8">
         <v>44593</v>
       </c>
-      <c r="B93" s="9">
+      <c r="B93" s="1">
+        <v>67765</v>
+      </c>
+      <c r="E93" s="1">
+        <v>3823</v>
+      </c>
+      <c r="F93" s="9">
         <v>16.87029768</v>
       </c>
-      <c r="C93" s="1">
+      <c r="H93" s="1">
+        <v>4468</v>
+      </c>
+      <c r="I93" s="1">
+        <v>15567</v>
+      </c>
+      <c r="J93" s="1">
         <v>62.67308531</v>
       </c>
-      <c r="G93" s="1">
-        <v>67765</v>
-      </c>
-      <c r="H93" s="1">
-        <v>3823</v>
+      <c r="O93" s="1">
+        <v>17.8303313</v>
+      </c>
+      <c r="P93" s="1">
+        <v>24.01521984</v>
+      </c>
+      <c r="Q93" s="1">
+        <v>26.1938861</v>
+      </c>
+      <c r="S93" s="9">
+        <v>16.87029768</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="8">
         <v>44621</v>
       </c>
-      <c r="B94" s="9">
+      <c r="B94" s="1">
+        <v>121207</v>
+      </c>
+      <c r="C94" s="1">
+        <v>233.8240135</v>
+      </c>
+      <c r="D94" s="1">
+        <v>1417.14408657</v>
+      </c>
+      <c r="E94" s="1">
+        <v>4131</v>
+      </c>
+      <c r="F94" s="9">
         <v>12.4513501</v>
       </c>
-      <c r="C94" s="1">
+      <c r="H94" s="1">
+        <v>10610</v>
+      </c>
+      <c r="I94" s="1">
+        <v>27531</v>
+      </c>
+      <c r="J94" s="1">
         <v>60.58287962</v>
       </c>
-      <c r="G94" s="1">
-        <v>121207</v>
-      </c>
-      <c r="H94" s="1">
-        <v>4131</v>
+      <c r="O94" s="1">
+        <v>10.99447323</v>
+      </c>
+      <c r="P94" s="1">
+        <v>23.02239884</v>
+      </c>
+      <c r="Q94" s="1">
+        <v>18.09093031</v>
+      </c>
+      <c r="R94" s="1">
+        <v>61409.66666667</v>
+      </c>
+      <c r="S94" s="9">
+        <v>12.4513501</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="8">
         <v>44652</v>
       </c>
-      <c r="B95" s="9">
+      <c r="B95" s="1">
+        <v>295095</v>
+      </c>
+      <c r="E95" s="1">
+        <v>5048</v>
+      </c>
+      <c r="F95" s="9">
         <v>7.34171785</v>
       </c>
-      <c r="C95" s="1">
+      <c r="H95" s="1">
+        <v>25319</v>
+      </c>
+      <c r="I95" s="1">
+        <v>41079</v>
+      </c>
+      <c r="J95" s="1">
         <v>66.39493782</v>
       </c>
-      <c r="G95" s="1">
-        <v>295095</v>
-      </c>
-      <c r="H95" s="1">
-        <v>5048</v>
+      <c r="O95" s="1">
+        <v>6.63301908</v>
+      </c>
+      <c r="P95" s="1">
+        <v>16.56200433</v>
+      </c>
+      <c r="Q95" s="1">
+        <v>12.43069999</v>
+      </c>
+      <c r="S95" s="9">
+        <v>7.34171785</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8">
         <v>44682</v>
       </c>
-      <c r="B96" s="9">
+      <c r="B96" s="1">
+        <v>418458</v>
+      </c>
+      <c r="E96" s="1">
+        <v>7150</v>
+      </c>
+      <c r="F96" s="9">
         <v>6.09692411</v>
       </c>
-      <c r="C96" s="1">
+      <c r="H96" s="1">
+        <v>43214</v>
+      </c>
+      <c r="I96" s="1">
+        <v>59198</v>
+      </c>
+      <c r="J96" s="1">
         <v>72.77220727</v>
       </c>
-      <c r="G96" s="1">
-        <v>418458</v>
-      </c>
-      <c r="H96" s="1">
-        <v>7150</v>
+      <c r="O96" s="1">
+        <v>4.41423587</v>
+      </c>
+      <c r="P96" s="1">
+        <v>12.51563707</v>
+      </c>
+      <c r="Q96" s="1">
+        <v>9.86904219</v>
+      </c>
+      <c r="S96" s="9">
+        <v>6.09692411</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="8">
         <v>44713</v>
       </c>
-      <c r="B97" s="9">
+      <c r="B97" s="1">
+        <v>543733</v>
+      </c>
+      <c r="C97" s="1">
+        <v>452.47565678</v>
+      </c>
+      <c r="D97" s="1">
+        <v>4572.52438757</v>
+      </c>
+      <c r="E97" s="1">
+        <v>10191</v>
+      </c>
+      <c r="F97" s="9">
         <v>5.6905102</v>
       </c>
-      <c r="C97" s="1">
+      <c r="H97" s="1">
+        <v>49878</v>
+      </c>
+      <c r="I97" s="1">
+        <v>64337</v>
+      </c>
+      <c r="J97" s="1">
         <v>78.07311692</v>
       </c>
-      <c r="G97" s="1">
-        <v>543733</v>
-      </c>
-      <c r="H97" s="1">
-        <v>10191</v>
+      <c r="O97" s="1">
+        <v>3.9136701</v>
+      </c>
+      <c r="P97" s="1">
+        <v>11.59725251</v>
+      </c>
+      <c r="Q97" s="1">
+        <v>10.84772398</v>
+      </c>
+      <c r="R97" s="1">
+        <v>61881.66666667</v>
+      </c>
+      <c r="S97" s="9">
+        <v>5.6905102</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8">
         <v>44743</v>
       </c>
-      <c r="B98" s="9">
+      <c r="B98" s="1">
+        <v>726739</v>
+      </c>
+      <c r="E98" s="1">
+        <v>16622</v>
+      </c>
+      <c r="F98" s="9">
         <v>5.12494991</v>
       </c>
-      <c r="C98" s="1">
+      <c r="H98" s="1">
+        <v>61575</v>
+      </c>
+      <c r="I98" s="1">
+        <v>75130</v>
+      </c>
+      <c r="J98" s="1">
         <v>79.14111572</v>
       </c>
-      <c r="G98" s="1">
-        <v>726739</v>
-      </c>
-      <c r="H98" s="1">
-        <v>16622</v>
+      <c r="O98" s="1">
+        <v>3.37759794</v>
+      </c>
+      <c r="P98" s="1">
+        <v>11.64519774</v>
+      </c>
+      <c r="Q98" s="1">
+        <v>8.67074751</v>
+      </c>
+      <c r="S98" s="9">
+        <v>5.12494991</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="8">
         <v>44774</v>
       </c>
-      <c r="B99" s="9">
+      <c r="B99" s="1">
+        <v>728744</v>
+      </c>
+      <c r="E99" s="1">
+        <v>14735</v>
+      </c>
+      <c r="F99" s="9">
         <v>4.87216315</v>
       </c>
-      <c r="C99" s="1">
+      <c r="H99" s="1">
+        <v>63905</v>
+      </c>
+      <c r="I99" s="1">
+        <v>76249</v>
+      </c>
+      <c r="J99" s="1">
         <v>77.14465378</v>
       </c>
-      <c r="G99" s="1">
-        <v>728744</v>
-      </c>
-      <c r="H99" s="1">
-        <v>14735</v>
+      <c r="O99" s="1">
+        <v>3.05086135</v>
+      </c>
+      <c r="P99" s="1">
+        <v>12.77938487</v>
+      </c>
+      <c r="Q99" s="1">
+        <v>7.76366906</v>
+      </c>
+      <c r="S99" s="9">
+        <v>4.87216315</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="8">
         <v>44805</v>
       </c>
-      <c r="B100" s="9">
+      <c r="B100" s="1">
+        <v>782215</v>
+      </c>
+      <c r="C100" s="1">
+        <v>663.51808303</v>
+      </c>
+      <c r="D100" s="1">
+        <v>9083.61939613</v>
+      </c>
+      <c r="E100" s="1">
+        <v>14127</v>
+      </c>
+      <c r="F100" s="9">
         <v>4.38206123</v>
       </c>
-      <c r="C100" s="1">
+      <c r="H100" s="1">
+        <v>81914</v>
+      </c>
+      <c r="I100" s="1">
+        <v>86393</v>
+      </c>
+      <c r="J100" s="1">
         <v>82.84273883</v>
       </c>
-      <c r="G100" s="1">
-        <v>782215</v>
-      </c>
-      <c r="H100" s="1">
-        <v>14127</v>
+      <c r="O100" s="1">
+        <v>2.77873363</v>
+      </c>
+      <c r="P100" s="1">
+        <v>10.76540284</v>
+      </c>
+      <c r="Q100" s="1">
+        <v>6.57913369</v>
+      </c>
+      <c r="R100" s="1">
+        <v>62442.66666667</v>
+      </c>
+      <c r="S100" s="9">
+        <v>4.38206123</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="8">
         <v>44835</v>
       </c>
-      <c r="B101" s="9">
+      <c r="B101" s="1">
+        <v>816833</v>
+      </c>
+      <c r="E101" s="1">
+        <v>14971</v>
+      </c>
+      <c r="F101" s="9">
         <v>4.38539838</v>
       </c>
-      <c r="C101" s="1">
+      <c r="H101" s="1">
+        <v>77092</v>
+      </c>
+      <c r="I101" s="1">
+        <v>81796</v>
+      </c>
+      <c r="J101" s="1">
         <v>84.43229195000001</v>
       </c>
-      <c r="G101" s="1">
-        <v>816833</v>
-      </c>
-      <c r="H101" s="1">
-        <v>14971</v>
+      <c r="O101" s="1">
+        <v>2.81492497</v>
+      </c>
+      <c r="P101" s="1">
+        <v>11.5664521</v>
+      </c>
+      <c r="Q101" s="1">
+        <v>6.78997458</v>
+      </c>
+      <c r="S101" s="9">
+        <v>4.38539838</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="8">
         <v>44866</v>
       </c>
-      <c r="B102" s="9">
+      <c r="B102" s="1">
+        <v>816340</v>
+      </c>
+      <c r="E102" s="1">
+        <v>16024</v>
+      </c>
+      <c r="F102" s="9">
         <v>4.1465637</v>
       </c>
-      <c r="C102" s="1">
+      <c r="H102" s="1">
+        <v>72305</v>
+      </c>
+      <c r="I102" s="1">
+        <v>73694</v>
+      </c>
+      <c r="J102" s="1">
         <v>85.82235138</v>
       </c>
-      <c r="G102" s="1">
-        <v>816340</v>
-      </c>
-      <c r="H102" s="1">
-        <v>16024</v>
+      <c r="O102" s="1">
+        <v>2.71639897</v>
+      </c>
+      <c r="P102" s="1">
+        <v>11.17219057</v>
+      </c>
+      <c r="Q102" s="1">
+        <v>6.9604147</v>
+      </c>
+      <c r="S102" s="9">
+        <v>4.1465637</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8">
         <v>44896</v>
       </c>
-      <c r="B103" s="9">
+      <c r="B103" s="1">
+        <v>931441</v>
+      </c>
+      <c r="C103" s="1">
+        <v>648.70496431</v>
+      </c>
+      <c r="D103" s="1">
+        <v>14177.70974938</v>
+      </c>
+      <c r="E103" s="1">
+        <v>19685</v>
+      </c>
+      <c r="F103" s="9">
         <v>4.16434421</v>
       </c>
-      <c r="C103" s="1">
+      <c r="G103" s="1">
+        <v>2248.38016725</v>
+      </c>
+      <c r="H103" s="1">
+        <v>95475</v>
+      </c>
+      <c r="I103" s="1">
+        <v>74067</v>
+      </c>
+      <c r="J103" s="1">
         <v>78.17278383999999</v>
       </c>
-      <c r="D103" s="1">
-        <v>2248.38016725</v>
-      </c>
-      <c r="E103" s="1">
-        <v>14177.70974938</v>
-      </c>
-      <c r="F103" s="1">
+      <c r="K103" s="1">
         <v>5.04255892</v>
       </c>
-      <c r="G103" s="1">
-        <v>931441</v>
-      </c>
-      <c r="H103" s="1">
-        <v>19685</v>
+      <c r="L103" s="1">
+        <v>4602.25632978</v>
+      </c>
+      <c r="M103" s="1">
+        <v>1553.55119165</v>
+      </c>
+      <c r="N103" s="1">
+        <v>1054.94843765</v>
+      </c>
+      <c r="O103" s="1">
+        <v>2.92232287</v>
+      </c>
+      <c r="P103" s="1">
+        <v>11.54956969</v>
+      </c>
+      <c r="Q103" s="1">
+        <v>7.15868164</v>
+      </c>
+      <c r="R103" s="1">
+        <v>61866.66666667</v>
+      </c>
+      <c r="S103" s="9">
+        <v>4.16434421</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8">
         <v>44927</v>
       </c>
-      <c r="B104" s="9">
+      <c r="B104" s="1">
+        <v>931814</v>
+      </c>
+      <c r="E104" s="1">
+        <v>28375</v>
+      </c>
+      <c r="F104" s="9">
         <v>4.32066786</v>
       </c>
-      <c r="C104" s="1">
+      <c r="H104" s="1">
+        <v>72756</v>
+      </c>
+      <c r="I104" s="1">
+        <v>56605</v>
+      </c>
+      <c r="J104" s="1">
         <v>71.27251631999999</v>
       </c>
-      <c r="G104" s="1">
-        <v>931814</v>
-      </c>
-      <c r="H104" s="1">
-        <v>28375</v>
+      <c r="O104" s="1">
+        <v>2.79847634</v>
+      </c>
+      <c r="P104" s="1">
+        <v>10.22573279</v>
+      </c>
+      <c r="Q104" s="1">
+        <v>8.20665391</v>
+      </c>
+      <c r="S104" s="9">
+        <v>4.32066786</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8">
         <v>44958</v>
       </c>
-      <c r="B105" s="9">
+      <c r="B105" s="1">
+        <v>957844</v>
+      </c>
+      <c r="E105" s="1">
+        <v>35312</v>
+      </c>
+      <c r="F105" s="9">
         <v>3.787811</v>
       </c>
-      <c r="C105" s="1">
+      <c r="H105" s="1">
+        <v>88040</v>
+      </c>
+      <c r="I105" s="1">
+        <v>61301</v>
+      </c>
+      <c r="J105" s="1">
         <v>85.08789048</v>
       </c>
-      <c r="G105" s="1">
-        <v>957844</v>
-      </c>
-      <c r="H105" s="1">
-        <v>35312</v>
+      <c r="O105" s="1">
+        <v>2.27667229</v>
+      </c>
+      <c r="P105" s="1">
+        <v>9.585500120000001</v>
+      </c>
+      <c r="Q105" s="1">
+        <v>6.75890327</v>
+      </c>
+      <c r="S105" s="9">
+        <v>3.787811</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8">
         <v>44986</v>
       </c>
-      <c r="B106" s="9">
+      <c r="B106" s="1">
+        <v>1021040</v>
+      </c>
+      <c r="C106" s="1">
+        <v>324.6529185</v>
+      </c>
+      <c r="D106" s="1">
+        <v>6017.94372289</v>
+      </c>
+      <c r="E106" s="1">
+        <v>60888</v>
+      </c>
+      <c r="F106" s="9">
         <v>3.79990501</v>
       </c>
-      <c r="C106" s="1">
+      <c r="H106" s="1">
+        <v>97835</v>
+      </c>
+      <c r="I106" s="1">
+        <v>75339</v>
+      </c>
+      <c r="J106" s="1">
         <v>80.04863102</v>
       </c>
-      <c r="G106" s="1">
-        <v>1021040</v>
-      </c>
-      <c r="H106" s="1">
-        <v>60888</v>
+      <c r="O106" s="1">
+        <v>2.51583126</v>
+      </c>
+      <c r="P106" s="1">
+        <v>6.87745288</v>
+      </c>
+      <c r="Q106" s="1">
+        <v>6.58766163</v>
+      </c>
+      <c r="R106" s="1">
+        <v>62784.66666667</v>
+      </c>
+      <c r="S106" s="9">
+        <v>3.79990501</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8">
         <v>45017</v>
       </c>
-      <c r="B107" s="9">
+      <c r="B107" s="1">
+        <v>1128610</v>
+      </c>
+      <c r="E107" s="1">
+        <v>90725</v>
+      </c>
+      <c r="F107" s="9">
         <v>3.7549784</v>
       </c>
-      <c r="C107" s="1">
+      <c r="H107" s="1">
+        <v>98190</v>
+      </c>
+      <c r="I107" s="1">
+        <v>97032</v>
+      </c>
+      <c r="J107" s="1">
         <v>78.97420137</v>
       </c>
-      <c r="G107" s="1">
-        <v>1128610</v>
-      </c>
-      <c r="H107" s="1">
-        <v>90725</v>
+      <c r="O107" s="1">
+        <v>2.30177724</v>
+      </c>
+      <c r="P107" s="1">
+        <v>5.48973675</v>
+      </c>
+      <c r="Q107" s="1">
+        <v>6.39423869</v>
+      </c>
+      <c r="S107" s="9">
+        <v>3.7549784</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8">
         <v>45047</v>
       </c>
-      <c r="B108" s="9">
+      <c r="B108" s="1">
+        <v>1112512</v>
+      </c>
+      <c r="E108" s="1">
+        <v>95613</v>
+      </c>
+      <c r="F108" s="9">
         <v>3.85334687</v>
       </c>
-      <c r="C108" s="1">
+      <c r="H108" s="1">
+        <v>98347</v>
+      </c>
+      <c r="I108" s="1">
+        <v>130444</v>
+      </c>
+      <c r="J108" s="1">
         <v>80.72367828</v>
       </c>
-      <c r="G108" s="1">
-        <v>1112512</v>
-      </c>
-      <c r="H108" s="1">
-        <v>95613</v>
+      <c r="O108" s="1">
+        <v>2.40482206</v>
+      </c>
+      <c r="P108" s="1">
+        <v>4.82016581</v>
+      </c>
+      <c r="Q108" s="1">
+        <v>6.66819216</v>
+      </c>
+      <c r="S108" s="9">
+        <v>3.85334687</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8">
         <v>45078</v>
       </c>
-      <c r="B109" s="9">
+      <c r="B109" s="1">
+        <v>1129310</v>
+      </c>
+      <c r="C109" s="1">
+        <v>172.19078824</v>
+      </c>
+      <c r="D109" s="1">
+        <v>12445.99017278</v>
+      </c>
+      <c r="E109" s="1">
+        <v>113290</v>
+      </c>
+      <c r="F109" s="9">
         <v>4.00308787</v>
       </c>
-      <c r="C109" s="1">
+      <c r="H109" s="1">
+        <v>85945</v>
+      </c>
+      <c r="I109" s="1">
+        <v>114588</v>
+      </c>
+      <c r="J109" s="1">
         <v>81.06717027000001</v>
       </c>
-      <c r="G109" s="1">
-        <v>1129310</v>
-      </c>
-      <c r="H109" s="1">
-        <v>113290</v>
+      <c r="O109" s="1">
+        <v>2.55386485</v>
+      </c>
+      <c r="P109" s="1">
+        <v>4.85558396</v>
+      </c>
+      <c r="Q109" s="1">
+        <v>7.6561253</v>
+      </c>
+      <c r="R109" s="1">
+        <v>63470.66666667</v>
+      </c>
+      <c r="S109" s="9">
+        <v>4.00308787</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="8">
         <v>45108</v>
       </c>
-      <c r="B110" s="9">
+      <c r="B110" s="1">
+        <v>1419642</v>
+      </c>
+      <c r="E110" s="1">
+        <v>231331</v>
+      </c>
+      <c r="F110" s="9">
         <v>3.81994859</v>
       </c>
-      <c r="C110" s="1">
+      <c r="H110" s="1">
+        <v>84876</v>
+      </c>
+      <c r="I110" s="1">
+        <v>93056</v>
+      </c>
+      <c r="J110" s="1">
         <v>90.29539758</v>
       </c>
-      <c r="G110" s="1">
-        <v>1419642</v>
-      </c>
-      <c r="H110" s="1">
-        <v>231331</v>
+      <c r="O110" s="1">
+        <v>2.51473386</v>
+      </c>
+      <c r="P110" s="1">
+        <v>4.78027612</v>
+      </c>
+      <c r="Q110" s="1">
+        <v>6.14473562</v>
+      </c>
+      <c r="S110" s="9">
+        <v>3.81994859</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8">
         <v>45139</v>
       </c>
-      <c r="B111" s="9">
+      <c r="B111" s="1">
+        <v>1312693</v>
+      </c>
+      <c r="E111" s="1">
+        <v>215442</v>
+      </c>
+      <c r="F111" s="9">
         <v>4.00239147</v>
       </c>
-      <c r="C111" s="1">
+      <c r="H111" s="1">
+        <v>88044</v>
+      </c>
+      <c r="I111" s="1">
+        <v>83601</v>
+      </c>
+      <c r="J111" s="1">
         <v>86.27374369</v>
       </c>
-      <c r="G111" s="1">
-        <v>1312693</v>
-      </c>
-      <c r="H111" s="1">
-        <v>215442</v>
+      <c r="O111" s="1">
+        <v>2.4383565</v>
+      </c>
+      <c r="P111" s="1">
+        <v>5.33281043</v>
+      </c>
+      <c r="Q111" s="1">
+        <v>6.54983861</v>
+      </c>
+      <c r="S111" s="9">
+        <v>4.00239147</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="8">
         <v>45170</v>
       </c>
-      <c r="B112" s="9">
+      <c r="B112" s="1">
+        <v>1130762</v>
+      </c>
+      <c r="C112" s="1">
+        <v>123.56254516</v>
+      </c>
+      <c r="D112" s="1">
+        <v>20307.57071465</v>
+      </c>
+      <c r="E112" s="1">
+        <v>135677</v>
+      </c>
+      <c r="F112" s="9">
         <v>3.65395109</v>
       </c>
-      <c r="C112" s="1">
+      <c r="H112" s="1">
+        <v>89384</v>
+      </c>
+      <c r="I112" s="1">
+        <v>81016</v>
+      </c>
+      <c r="J112" s="1">
         <v>82.67366269</v>
       </c>
-      <c r="G112" s="1">
-        <v>1130762</v>
-      </c>
-      <c r="H112" s="1">
-        <v>135677</v>
+      <c r="O112" s="1">
+        <v>2.36599523</v>
+      </c>
+      <c r="P112" s="1">
+        <v>4.60880867</v>
+      </c>
+      <c r="Q112" s="1">
+        <v>6.14521858</v>
+      </c>
+      <c r="R112" s="1">
+        <v>64811.33333333</v>
+      </c>
+      <c r="S112" s="9">
+        <v>3.65395109</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="8">
         <v>45200</v>
       </c>
-      <c r="B113" s="9">
+      <c r="B113" s="1">
+        <v>1125964</v>
+      </c>
+      <c r="E113" s="1">
+        <v>122765</v>
+      </c>
+      <c r="F113" s="9">
         <v>3.55358812</v>
       </c>
-      <c r="C113" s="1">
+      <c r="H113" s="1">
+        <v>88643</v>
+      </c>
+      <c r="I113" s="1">
+        <v>94334</v>
+      </c>
+      <c r="J113" s="1">
         <v>77.66917522</v>
       </c>
-      <c r="G113" s="1">
-        <v>1125964</v>
-      </c>
-      <c r="H113" s="1">
-        <v>122765</v>
+      <c r="O113" s="1">
+        <v>2.31876959</v>
+      </c>
+      <c r="P113" s="1">
+        <v>4.34861254</v>
+      </c>
+      <c r="Q113" s="1">
+        <v>5.7968085</v>
+      </c>
+      <c r="S113" s="9">
+        <v>3.55358812</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="8">
         <v>45231</v>
       </c>
-      <c r="B114" s="9">
+      <c r="B114" s="1">
+        <v>1100459</v>
+      </c>
+      <c r="E114" s="1">
+        <v>104347</v>
+      </c>
+      <c r="F114" s="9">
         <v>3.41625483</v>
       </c>
-      <c r="C114" s="1">
+      <c r="H114" s="1">
+        <v>93414</v>
+      </c>
+      <c r="I114" s="1">
+        <v>90231</v>
+      </c>
+      <c r="J114" s="1">
         <v>78.29516881000001</v>
       </c>
-      <c r="G114" s="1">
-        <v>1100459</v>
-      </c>
-      <c r="H114" s="1">
-        <v>104347</v>
+      <c r="O114" s="1">
+        <v>2.26994822</v>
+      </c>
+      <c r="P114" s="1">
+        <v>4.2007359</v>
+      </c>
+      <c r="Q114" s="1">
+        <v>5.67959151</v>
+      </c>
+      <c r="S114" s="9">
+        <v>3.41625483</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="8">
         <v>45261</v>
       </c>
-      <c r="B115" s="9">
+      <c r="B115" s="1">
+        <v>1231565</v>
+      </c>
+      <c r="C115" s="1">
+        <v>91.53661993</v>
+      </c>
+      <c r="D115" s="1">
+        <v>27155.50603753</v>
+      </c>
+      <c r="E115" s="1">
+        <v>130156</v>
+      </c>
+      <c r="F115" s="9">
         <v>3.54934946</v>
       </c>
-      <c r="C115" s="1">
+      <c r="G115" s="1">
+        <v>1995.2781706</v>
+      </c>
+      <c r="H115" s="1">
+        <v>102683</v>
+      </c>
+      <c r="I115" s="1">
+        <v>92620</v>
+      </c>
+      <c r="J115" s="1">
         <v>73.94906972</v>
       </c>
-      <c r="D115" s="1">
-        <v>1995.2781706</v>
-      </c>
-      <c r="E115" s="1">
-        <v>27155.50603753</v>
-      </c>
-      <c r="F115" s="1">
+      <c r="K115" s="1">
         <v>3.791459</v>
       </c>
-      <c r="G115" s="1">
-        <v>1231565</v>
-      </c>
-      <c r="H115" s="1">
-        <v>130156</v>
+      <c r="L115" s="1">
+        <v>2262.59838018</v>
+      </c>
+      <c r="M115" s="1">
+        <v>1419.04775716</v>
+      </c>
+      <c r="N115" s="1">
+        <v>830.1138089</v>
+      </c>
+      <c r="O115" s="1">
+        <v>2.48626826</v>
+      </c>
+      <c r="P115" s="1">
+        <v>4.05690972</v>
+      </c>
+      <c r="Q115" s="1">
+        <v>5.99824954</v>
+      </c>
+      <c r="R115" s="1">
+        <v>65616.66666667</v>
+      </c>
+      <c r="S115" s="9">
+        <v>3.54934946</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8">
         <v>45292</v>
       </c>
-      <c r="B116" s="9">
+      <c r="B116" s="1">
+        <v>1419956</v>
+      </c>
+      <c r="E116" s="1">
+        <v>211150</v>
+      </c>
+      <c r="F116" s="9">
         <v>3.49473239</v>
       </c>
-      <c r="C116" s="1">
+      <c r="H116" s="1">
+        <v>93442</v>
+      </c>
+      <c r="I116" s="1">
+        <v>82113</v>
+      </c>
+      <c r="J116" s="1">
         <v>78.01252826</v>
       </c>
-      <c r="G116" s="1">
-        <v>1419956</v>
-      </c>
-      <c r="H116" s="1">
-        <v>211150</v>
+      <c r="O116" s="1">
+        <v>2.27594092</v>
+      </c>
+      <c r="P116" s="1">
+        <v>3.73459775</v>
+      </c>
+      <c r="Q116" s="1">
+        <v>6.25357588</v>
+      </c>
+      <c r="S116" s="9">
+        <v>3.49473239</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="8">
         <v>45323</v>
       </c>
-      <c r="B117" s="9">
+      <c r="B117" s="1">
+        <v>1417807</v>
+      </c>
+      <c r="E117" s="1">
+        <v>326860</v>
+      </c>
+      <c r="F117" s="9">
         <v>3.50327036</v>
       </c>
-      <c r="C117" s="1">
+      <c r="H117" s="1">
+        <v>100081</v>
+      </c>
+      <c r="I117" s="1">
+        <v>66149</v>
+      </c>
+      <c r="J117" s="1">
         <v>83.19153921</v>
       </c>
-      <c r="G117" s="1">
-        <v>1417807</v>
-      </c>
-      <c r="H117" s="1">
-        <v>326860</v>
+      <c r="O117" s="1">
+        <v>2.09125512</v>
+      </c>
+      <c r="P117" s="1">
+        <v>4.22584291</v>
+      </c>
+      <c r="Q117" s="1">
+        <v>6.37243048</v>
+      </c>
+      <c r="S117" s="9">
+        <v>3.50327036</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="8">
         <v>45352</v>
       </c>
-      <c r="B118" s="9">
+      <c r="B118" s="1">
+        <v>1464865</v>
+      </c>
+      <c r="C118" s="1">
+        <v>34.21807233</v>
+      </c>
+      <c r="D118" s="1">
+        <v>8077.16805887</v>
+      </c>
+      <c r="E118" s="1">
+        <v>247622</v>
+      </c>
+      <c r="F118" s="9">
         <v>3.33834727</v>
       </c>
-      <c r="C118" s="1">
+      <c r="H118" s="1">
+        <v>120283</v>
+      </c>
+      <c r="I118" s="1">
+        <v>97026</v>
+      </c>
+      <c r="J118" s="1">
         <v>83.41271879</v>
       </c>
-      <c r="G118" s="1">
-        <v>1464865</v>
-      </c>
-      <c r="H118" s="1">
-        <v>247622</v>
+      <c r="O118" s="1">
+        <v>1.96720314</v>
+      </c>
+      <c r="P118" s="1">
+        <v>3.62329067</v>
+      </c>
+      <c r="Q118" s="1">
+        <v>5.89130193</v>
+      </c>
+      <c r="R118" s="1">
+        <v>66284.33333333</v>
+      </c>
+      <c r="S118" s="9">
+        <v>3.33834727</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="8">
         <v>45383</v>
       </c>
-      <c r="B119" s="9">
+      <c r="B119" s="1">
+        <v>1343319</v>
+      </c>
+      <c r="E119" s="1">
+        <v>220332</v>
+      </c>
+      <c r="F119" s="9">
         <v>3.4328891</v>
       </c>
-      <c r="C119" s="1">
+      <c r="H119" s="1">
+        <v>106248</v>
+      </c>
+      <c r="I119" s="1">
+        <v>106694</v>
+      </c>
+      <c r="J119" s="1">
         <v>77.96882822000001</v>
       </c>
-      <c r="G119" s="1">
-        <v>1343319</v>
-      </c>
-      <c r="H119" s="1">
-        <v>220332</v>
+      <c r="O119" s="1">
+        <v>2.06099727</v>
+      </c>
+      <c r="P119" s="1">
+        <v>3.37354174</v>
+      </c>
+      <c r="Q119" s="1">
+        <v>6.12401057</v>
+      </c>
+      <c r="S119" s="9">
+        <v>3.4328891</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8">
         <v>45413</v>
       </c>
-      <c r="B120" s="9">
+      <c r="B120" s="1">
+        <v>1277160</v>
+      </c>
+      <c r="E120" s="1">
+        <v>222010</v>
+      </c>
+      <c r="F120" s="9">
         <v>3.70187269</v>
       </c>
-      <c r="C120" s="1">
+      <c r="H120" s="1">
+        <v>95761</v>
+      </c>
+      <c r="I120" s="1">
+        <v>156517</v>
+      </c>
+      <c r="J120" s="1">
         <v>78.76344845</v>
       </c>
-      <c r="G120" s="1">
-        <v>1277160</v>
-      </c>
-      <c r="H120" s="1">
-        <v>222010</v>
+      <c r="O120" s="1">
+        <v>2.26150037</v>
+      </c>
+      <c r="P120" s="1">
+        <v>3.38423561</v>
+      </c>
+      <c r="Q120" s="1">
+        <v>6.55430914</v>
+      </c>
+      <c r="S120" s="9">
+        <v>3.70187269</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="8">
         <v>45444</v>
       </c>
-      <c r="B121" s="9">
+      <c r="B121" s="1">
+        <v>1250293</v>
+      </c>
+      <c r="C121" s="1">
+        <v>19.90491324</v>
+      </c>
+      <c r="D121" s="1">
+        <v>14923.35371873</v>
+      </c>
+      <c r="E121" s="1">
+        <v>216170</v>
+      </c>
+      <c r="F121" s="9">
         <v>3.79600444</v>
       </c>
-      <c r="C121" s="1">
+      <c r="H121" s="1">
+        <v>83913</v>
+      </c>
+      <c r="I121" s="1">
+        <v>120009</v>
+      </c>
+      <c r="J121" s="1">
         <v>76.91959518</v>
       </c>
-      <c r="G121" s="1">
-        <v>1250293</v>
-      </c>
-      <c r="H121" s="1">
-        <v>216170</v>
+      <c r="O121" s="1">
+        <v>2.38565655</v>
+      </c>
+      <c r="P121" s="1">
+        <v>3.56395322</v>
+      </c>
+      <c r="Q121" s="1">
+        <v>7.16093957</v>
+      </c>
+      <c r="R121" s="1">
+        <v>66998</v>
+      </c>
+      <c r="S121" s="9">
+        <v>3.79600444</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="8">
         <v>45474</v>
       </c>
-      <c r="B122" s="9">
+      <c r="B122" s="1">
+        <v>1602603</v>
+      </c>
+      <c r="E122" s="1">
+        <v>412805</v>
+      </c>
+      <c r="F122" s="9">
         <v>3.66469904</v>
       </c>
-      <c r="C122" s="1">
+      <c r="H122" s="1">
+        <v>83146</v>
+      </c>
+      <c r="I122" s="1">
+        <v>89642</v>
+      </c>
+      <c r="J122" s="1">
         <v>89.38596473</v>
       </c>
-      <c r="G122" s="1">
-        <v>1602603</v>
-      </c>
-      <c r="H122" s="1">
-        <v>412805</v>
+      <c r="O122" s="1">
+        <v>2.39030625</v>
+      </c>
+      <c r="P122" s="1">
+        <v>3.83527092</v>
+      </c>
+      <c r="Q122" s="1">
+        <v>6.15066188</v>
+      </c>
+      <c r="S122" s="9">
+        <v>3.66469904</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="8">
         <v>45505</v>
       </c>
-      <c r="B123" s="9">
+      <c r="B123" s="1">
+        <v>1539828</v>
+      </c>
+      <c r="E123" s="1">
+        <v>403138</v>
+      </c>
+      <c r="F123" s="9">
         <v>3.6975754</v>
       </c>
-      <c r="C123" s="1">
+      <c r="H123" s="1">
+        <v>79895</v>
+      </c>
+      <c r="I123" s="1">
+        <v>91805</v>
+      </c>
+      <c r="J123" s="1">
         <v>87.84829851000001</v>
       </c>
-      <c r="G123" s="1">
-        <v>1539828</v>
-      </c>
-      <c r="H123" s="1">
-        <v>403138</v>
+      <c r="O123" s="1">
+        <v>2.33448834</v>
+      </c>
+      <c r="P123" s="1">
+        <v>4.09234657</v>
+      </c>
+      <c r="Q123" s="1">
+        <v>6.23281775</v>
+      </c>
+      <c r="S123" s="9">
+        <v>3.6975754</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="8">
         <v>45536</v>
       </c>
-      <c r="B124" s="9">
+      <c r="B124" s="1">
+        <v>1270681</v>
+      </c>
+      <c r="C124" s="1">
+        <v>10.40729671</v>
+      </c>
+      <c r="D124" s="1">
+        <v>22421.03985439</v>
+      </c>
+      <c r="E124" s="1">
+        <v>217205</v>
+      </c>
+      <c r="F124" s="9">
         <v>3.55457963</v>
       </c>
-      <c r="C124" s="1">
+      <c r="H124" s="1">
+        <v>112151</v>
+      </c>
+      <c r="I124" s="1">
+        <v>87767</v>
+      </c>
+      <c r="J124" s="1">
         <v>83.09800989</v>
       </c>
-      <c r="G124" s="1">
-        <v>1270681</v>
-      </c>
-      <c r="H124" s="1">
-        <v>217205</v>
+      <c r="O124" s="1">
+        <v>2.042768</v>
+      </c>
+      <c r="P124" s="1">
+        <v>3.9083079</v>
+      </c>
+      <c r="Q124" s="1">
+        <v>6.26460746</v>
+      </c>
+      <c r="R124" s="1">
+        <v>67005.33333333</v>
+      </c>
+      <c r="S124" s="9">
+        <v>3.55457963</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="8">
         <v>45566</v>
       </c>
-      <c r="B125" s="9">
+      <c r="B125" s="1">
+        <v>1314493</v>
+      </c>
+      <c r="E125" s="1">
+        <v>234528</v>
+      </c>
+      <c r="F125" s="9">
         <v>3.48693737</v>
       </c>
-      <c r="C125" s="1">
+      <c r="H125" s="1">
+        <v>103432</v>
+      </c>
+      <c r="I125" s="1">
+        <v>102233</v>
+      </c>
+      <c r="J125" s="1">
         <v>81.17976197999999</v>
       </c>
-      <c r="G125" s="1">
-        <v>1314493</v>
-      </c>
-      <c r="H125" s="1">
-        <v>234528</v>
+      <c r="O125" s="1">
+        <v>2.09070013</v>
+      </c>
+      <c r="P125" s="1">
+        <v>3.70378988</v>
+      </c>
+      <c r="Q125" s="1">
+        <v>5.95284111</v>
+      </c>
+      <c r="S125" s="9">
+        <v>3.48693737</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8">
         <v>45597</v>
       </c>
-      <c r="B126" s="9">
+      <c r="B126" s="1">
+        <v>1234698</v>
+      </c>
+      <c r="E126" s="1">
+        <v>174751</v>
+      </c>
+      <c r="F126" s="9">
         <v>3.53702158</v>
       </c>
-      <c r="C126" s="1">
+      <c r="H126" s="1">
+        <v>101920</v>
+      </c>
+      <c r="I126" s="1">
+        <v>92905</v>
+      </c>
+      <c r="J126" s="1">
         <v>81.71282475</v>
       </c>
-      <c r="G126" s="1">
-        <v>1234698</v>
-      </c>
-      <c r="H126" s="1">
-        <v>174751</v>
+      <c r="O126" s="1">
+        <v>2.17807121</v>
+      </c>
+      <c r="P126" s="1">
+        <v>3.85279436</v>
+      </c>
+      <c r="Q126" s="1">
+        <v>6.21534217</v>
+      </c>
+      <c r="S126" s="9">
+        <v>3.53702158</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="8">
         <v>45627</v>
       </c>
-      <c r="B127" s="9">
+      <c r="B127" s="1">
+        <v>1390641</v>
+      </c>
+      <c r="C127" s="1">
+        <v>9.668627799999999</v>
+      </c>
+      <c r="D127" s="1">
+        <v>29781.07084459</v>
+      </c>
+      <c r="E127" s="1">
+        <v>193483</v>
+      </c>
+      <c r="F127" s="9">
         <v>3.49854894</v>
       </c>
-      <c r="C127" s="1">
+      <c r="G127" s="1">
+        <v>1802.03624253</v>
+      </c>
+      <c r="H127" s="1">
+        <v>105622</v>
+      </c>
+      <c r="I127" s="1">
+        <v>103740</v>
+      </c>
+      <c r="J127" s="1">
         <v>75.11278097</v>
       </c>
-      <c r="D127" s="1">
-        <v>1802.03624253</v>
-      </c>
-      <c r="E127" s="1">
-        <v>29781.07084459</v>
-      </c>
-      <c r="F127" s="1">
+      <c r="K127" s="1">
         <v>3.55805608</v>
       </c>
-      <c r="G127" s="1">
-        <v>1390641</v>
-      </c>
-      <c r="H127" s="1">
-        <v>193483</v>
+      <c r="L127" s="1">
+        <v>1485.62882882</v>
+      </c>
+      <c r="M127" s="1">
+        <v>1239.45337328</v>
+      </c>
+      <c r="N127" s="1">
+        <v>761.8738805</v>
+      </c>
+      <c r="O127" s="1">
+        <v>2.28419878</v>
+      </c>
+      <c r="P127" s="1">
+        <v>3.70178189</v>
+      </c>
+      <c r="Q127" s="1">
+        <v>6.23567603</v>
+      </c>
+      <c r="R127" s="1">
+        <v>67065</v>
+      </c>
+      <c r="S127" s="9">
+        <v>3.49854894</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="8">
         <v>45658</v>
       </c>
-      <c r="B128" s="9">
-        <v>3.52215423</v>
-      </c>
-      <c r="C128" s="9">
+      <c r="B128" s="1">
+        <v>1633495</v>
+      </c>
+      <c r="E128" s="1">
+        <v>376481</v>
+      </c>
+      <c r="F128" s="9">
+        <v>3.52215261</v>
+      </c>
+      <c r="H128" s="1">
+        <v>102328</v>
+      </c>
+      <c r="I128" s="1">
+        <v>85400</v>
+      </c>
+      <c r="J128" s="9">
         <v>81.80868991</v>
       </c>
-      <c r="G128" s="1">
-        <v>1633495</v>
-      </c>
-      <c r="H128" s="1">
-        <v>376481</v>
+      <c r="O128" s="1">
+        <v>2.00461298</v>
+      </c>
+      <c r="P128" s="1">
+        <v>3.66224491</v>
+      </c>
+      <c r="Q128" s="1">
+        <v>6.74405782</v>
+      </c>
+      <c r="S128" s="9">
+        <v>3.52215261</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="8">
         <v>45689</v>
       </c>
-      <c r="B129" s="9">
-        <v>3.46523629</v>
-      </c>
-      <c r="C129" s="9">
+      <c r="B129" s="1">
+        <v>1377513</v>
+      </c>
+      <c r="E129" s="1">
+        <v>267974</v>
+      </c>
+      <c r="F129" s="9">
+        <v>3.46523707</v>
+      </c>
+      <c r="H129" s="1">
+        <v>105762</v>
+      </c>
+      <c r="I129" s="1">
+        <v>74869</v>
+      </c>
+      <c r="J129" s="9">
         <v>83.82109185</v>
       </c>
-      <c r="G129" s="1">
-        <v>1377513</v>
-      </c>
-      <c r="H129" s="1">
-        <v>267974</v>
+      <c r="O129" s="1">
+        <v>1.99470479</v>
+      </c>
+      <c r="P129" s="1">
+        <v>4.16446724</v>
+      </c>
+      <c r="Q129" s="1">
+        <v>6.60559892</v>
+      </c>
+      <c r="S129" s="9">
+        <v>3.46523707</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="8">
         <v>45717</v>
       </c>
-      <c r="B130" s="9">
+      <c r="B130" s="1">
+        <v>1296605</v>
+      </c>
+      <c r="C130" s="10">
+        <v>-0.84474375</v>
+      </c>
+      <c r="D130" s="1">
+        <v>8008.93668644</v>
+      </c>
+      <c r="E130" s="1">
+        <v>187036</v>
+      </c>
+      <c r="F130" s="9">
         <v>3.46429945</v>
       </c>
-      <c r="C130" s="9">
+      <c r="H130" s="1">
+        <v>104150</v>
+      </c>
+      <c r="I130" s="1">
+        <v>101198</v>
+      </c>
+      <c r="J130" s="9">
         <v>76.14225854999999</v>
       </c>
-      <c r="G130" s="1">
-        <v>1296605</v>
-      </c>
-      <c r="H130" s="1">
-        <v>187036</v>
+      <c r="O130" s="1">
+        <v>2.00872519</v>
+      </c>
+      <c r="P130" s="1">
+        <v>4.01373124</v>
+      </c>
+      <c r="Q130" s="1">
+        <v>6.01776113</v>
+      </c>
+      <c r="R130" s="1">
+        <v>66889</v>
+      </c>
+      <c r="S130" s="9">
+        <v>3.46429945</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="8">
         <v>45748</v>
       </c>
-      <c r="B131" s="9">
+      <c r="B131" s="1">
+        <v>1403644</v>
+      </c>
+      <c r="E131" s="1">
+        <v>207505</v>
+      </c>
+      <c r="F131" s="9">
         <v>3.43092325</v>
       </c>
-      <c r="C131" s="9">
+      <c r="H131" s="1">
+        <v>109253</v>
+      </c>
+      <c r="I131" s="1">
+        <v>118660</v>
+      </c>
+      <c r="J131" s="9">
         <v>78.53806025999999</v>
       </c>
-      <c r="G131" s="1">
-        <v>1403644</v>
-      </c>
-      <c r="H131" s="1">
-        <v>207505</v>
+      <c r="O131" s="1">
+        <v>1.91426363</v>
+      </c>
+      <c r="P131" s="1">
+        <v>3.67158026</v>
+      </c>
+      <c r="Q131" s="1">
+        <v>6.15319018</v>
+      </c>
+      <c r="S131" s="9">
+        <v>3.43092325</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="8">
         <v>45778</v>
       </c>
-      <c r="B132" s="9">
-        <v>3.56004101</v>
-      </c>
-      <c r="C132" s="9">
+      <c r="B132" s="1">
+        <v>1374170</v>
+      </c>
+      <c r="E132" s="1">
+        <v>242013</v>
+      </c>
+      <c r="F132" s="9">
+        <v>3.56003864</v>
+      </c>
+      <c r="H132" s="1">
+        <v>111673</v>
+      </c>
+      <c r="I132" s="1">
+        <v>154403</v>
+      </c>
+      <c r="J132" s="9">
         <v>79.57640013</v>
       </c>
-      <c r="G132" s="1">
-        <v>1374170</v>
-      </c>
-      <c r="H132" s="1">
-        <v>242013</v>
+      <c r="O132" s="1">
+        <v>2.0830882</v>
+      </c>
+      <c r="P132" s="1">
+        <v>3.37879414</v>
+      </c>
+      <c r="Q132" s="1">
+        <v>6.3695993</v>
+      </c>
+      <c r="S132" s="9">
+        <v>3.56003864</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="8">
         <v>45809</v>
       </c>
-      <c r="B133" s="9">
+      <c r="B133" s="1">
+        <v>1245947</v>
+      </c>
+      <c r="C133" s="1">
+        <v>4.49414317</v>
+      </c>
+      <c r="D133" s="1">
+        <v>15594.03060042</v>
+      </c>
+      <c r="E133" s="1">
+        <v>197185</v>
+      </c>
+      <c r="F133" s="9">
         <v>3.70343892</v>
       </c>
-      <c r="C133" s="9">
+      <c r="H133" s="1">
+        <v>100986</v>
+      </c>
+      <c r="I133" s="1">
+        <v>112726</v>
+      </c>
+      <c r="J133" s="9">
         <v>75.02096415</v>
       </c>
-      <c r="G133" s="1">
-        <v>1245947</v>
-      </c>
-      <c r="H133" s="1">
-        <v>197185</v>
+      <c r="O133" s="1">
+        <v>2.05586066</v>
+      </c>
+      <c r="P133" s="1">
+        <v>3.67407789</v>
+      </c>
+      <c r="Q133" s="1">
+        <v>7.1556167</v>
+      </c>
+      <c r="R133" s="1">
+        <v>67100.66666667</v>
+      </c>
+      <c r="S133" s="9">
+        <v>3.70343892</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="8">
         <v>45839</v>
       </c>
-      <c r="B134" s="9">
+      <c r="B134" s="1">
+        <v>1680771</v>
+      </c>
+      <c r="E134" s="1">
+        <v>414488</v>
+      </c>
+      <c r="F134" s="9">
         <v>3.49187013</v>
       </c>
-      <c r="C134" s="9">
+      <c r="H134" s="1">
+        <v>88384</v>
+      </c>
+      <c r="I134" s="1">
+        <v>85791</v>
+      </c>
+      <c r="J134" s="9">
         <v>91.25111715</v>
       </c>
-      <c r="G134" s="1">
-        <v>1680771</v>
-      </c>
-      <c r="H134" s="1">
-        <v>414488</v>
+      <c r="O134" s="1">
+        <v>2.13174811</v>
+      </c>
+      <c r="P134" s="1">
+        <v>3.64244655</v>
+      </c>
+      <c r="Q134" s="1">
+        <v>6.40779093</v>
+      </c>
+      <c r="S134" s="9">
+        <v>3.49187013</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="8">
         <v>45870</v>
       </c>
-      <c r="B135" s="9">
+      <c r="B135" s="1">
+        <v>1609320</v>
+      </c>
+      <c r="E135" s="1">
+        <v>398206</v>
+      </c>
+      <c r="F135" s="9">
         <v>3.60829522</v>
       </c>
-      <c r="C135" s="9">
+      <c r="H135" s="1">
+        <v>88675</v>
+      </c>
+      <c r="I135" s="1">
+        <v>91142</v>
+      </c>
+      <c r="J135" s="9">
         <v>89.55990068</v>
       </c>
-      <c r="G135" s="1">
-        <v>1609320</v>
-      </c>
-      <c r="H135" s="1">
-        <v>398206</v>
+      <c r="O135" s="1">
+        <v>2.17690603</v>
+      </c>
+      <c r="P135" s="1">
+        <v>3.95520563</v>
+      </c>
+      <c r="Q135" s="1">
+        <v>6.26300323</v>
+      </c>
+      <c r="S135" s="9">
+        <v>3.60829522</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="8">
         <v>45901</v>
       </c>
-      <c r="B136" s="9">
+      <c r="B136" s="1">
+        <v>1254346</v>
+      </c>
+      <c r="C136" s="1">
+        <v>6.5134349</v>
+      </c>
+      <c r="D136" s="1">
+        <v>23881.41968916</v>
+      </c>
+      <c r="E136" s="1">
+        <v>207028</v>
+      </c>
+      <c r="F136" s="9">
         <v>3.38601772</v>
       </c>
-      <c r="C136" s="9">
+      <c r="H136" s="1">
+        <v>120634</v>
+      </c>
+      <c r="I136" s="1">
+        <v>99038</v>
+      </c>
+      <c r="J136" s="9">
         <v>80.96374383</v>
       </c>
-      <c r="G136" s="1">
-        <v>1254346</v>
-      </c>
-      <c r="H136" s="1">
-        <v>207028</v>
+      <c r="O136" s="1">
+        <v>1.80390036</v>
+      </c>
+      <c r="P136" s="1">
+        <v>3.74071766</v>
+      </c>
+      <c r="Q136" s="1">
+        <v>5.76897962</v>
+      </c>
+      <c r="R136" s="1">
+        <v>67311.33333333</v>
+      </c>
+      <c r="S136" s="9">
+        <v>3.38601772</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="8">
         <v>45931</v>
       </c>
-      <c r="B137" s="9">
+      <c r="B137" s="1">
+        <v>1379077</v>
+      </c>
+      <c r="E137" s="1">
+        <v>226010</v>
+      </c>
+      <c r="F137" s="9">
         <v>3.37730347</v>
       </c>
-      <c r="C137" s="9">
+      <c r="H137" s="1">
+        <v>110303</v>
+      </c>
+      <c r="I137" s="1">
+        <v>103054</v>
+      </c>
+      <c r="J137" s="9">
         <v>84.69603788000001</v>
       </c>
-      <c r="G137" s="1">
-        <v>1379077</v>
-      </c>
-      <c r="H137" s="1">
-        <v>226010</v>
+      <c r="O137" s="1">
+        <v>1.974291</v>
+      </c>
+      <c r="P137" s="1">
+        <v>3.42315278</v>
+      </c>
+      <c r="Q137" s="1">
+        <v>5.46639757</v>
+      </c>
+      <c r="S137" s="9">
+        <v>3.37730347</v>
       </c>
     </row>
     <row r="138">
@@ -3147,36 +6491,75 @@
         <v>45962</v>
       </c>
       <c r="B138" s="9">
+        <v>1293402</v>
+      </c>
+      <c r="E138" s="9">
+        <v>203532</v>
+      </c>
+      <c r="F138" s="9">
         <v>3.29827077</v>
       </c>
-      <c r="C138" s="9">
+      <c r="H138" s="1">
+        <v>117163</v>
+      </c>
+      <c r="I138" s="1">
+        <v>84252</v>
+      </c>
+      <c r="J138" s="9">
         <v>84.95384722999999</v>
       </c>
-      <c r="G138" s="1">
-        <v>1293401</v>
-      </c>
-      <c r="H138" s="1">
-        <v>203531</v>
+      <c r="O138" s="1">
+        <v>1.9374895</v>
+      </c>
+      <c r="P138" s="1">
+        <v>3.55418573</v>
+      </c>
+      <c r="Q138" s="1">
+        <v>5.78551362</v>
+      </c>
+      <c r="S138" s="9">
+        <v>3.29827077</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="8">
         <v>45992</v>
       </c>
-      <c r="B139" s="9">
+      <c r="B139" s="1">
+        <v>1363999</v>
+      </c>
+      <c r="E139" s="1">
+        <v>172688</v>
+      </c>
+      <c r="F139" s="9">
         <v>3.47177136</v>
       </c>
-      <c r="C139" s="9">
+      <c r="H139" s="1">
+        <v>116067</v>
+      </c>
+      <c r="I139" s="1">
+        <v>96629</v>
+      </c>
+      <c r="J139" s="9">
         <v>76.44595653</v>
       </c>
-      <c r="F139" s="9">
-        <v>3.48480057</v>
-      </c>
-      <c r="G139" s="9">
-        <v>1363999</v>
-      </c>
-      <c r="H139" s="9">
-        <v>172688</v>
+      <c r="K139" s="9">
+        <v>3.48480029</v>
+      </c>
+      <c r="O139" s="1">
+        <v>2.14279833</v>
+      </c>
+      <c r="P139" s="1">
+        <v>3.85426758</v>
+      </c>
+      <c r="Q139" s="1">
+        <v>6.14510936</v>
+      </c>
+      <c r="R139" s="1">
+        <v>67108.66666667</v>
+      </c>
+      <c r="S139" s="9">
+        <v>3.47177136</v>
       </c>
     </row>
     <row r="140">
@@ -3184,16 +6567,66 @@
         <v>46023</v>
       </c>
       <c r="B140" s="9">
-        <v>3.43209009</v>
-      </c>
-      <c r="C140" s="9">
+        <v>1501426</v>
+      </c>
+      <c r="E140" s="1">
+        <v>271953</v>
+      </c>
+      <c r="F140" s="9">
+        <v>3.43208671</v>
+      </c>
+      <c r="H140" s="1">
+        <v>116682</v>
+      </c>
+      <c r="I140" s="9">
+        <v>85996</v>
+      </c>
+      <c r="J140" s="9">
         <v>81.17069512</v>
       </c>
-      <c r="G140" s="9">
-        <v>1501420</v>
-      </c>
-      <c r="H140" s="9">
-        <v>271953</v>
+      <c r="O140" s="1">
+        <v>1.8791539</v>
+      </c>
+      <c r="P140" s="1">
+        <v>3.49875582</v>
+      </c>
+      <c r="Q140" s="9">
+        <v>6.12521251</v>
+      </c>
+      <c r="S140" s="9">
+        <v>3.43208671</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8">
+        <v>46054</v>
+      </c>
+      <c r="B141" s="9">
+        <v>1500988</v>
+      </c>
+      <c r="E141" s="9">
+        <v>432327</v>
+      </c>
+      <c r="F141" s="9">
+        <v>3.38646648</v>
+      </c>
+      <c r="H141" s="9">
+        <v>90210</v>
+      </c>
+      <c r="I141" s="9">
+        <v>65040</v>
+      </c>
+      <c r="O141" s="9">
+        <v>1.967696</v>
+      </c>
+      <c r="P141" s="9">
+        <v>3.68987318</v>
+      </c>
+      <c r="Q141" s="9">
+        <v>6.22141812</v>
+      </c>
+      <c r="S141" s="9">
+        <v>3.38646648</v>
       </c>
     </row>
   </sheetData>
